--- a/docs/KARTOCHKI-OPISANIYA.xlsx
+++ b/docs/KARTOCHKI-OPISANIYA.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Препараты сайта" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сейчас на сайте" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="После загрузки CSV" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -58,7 +59,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -428,14 +429,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E88"/>
+  <dimension ref="A1:M88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="95" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -451,15 +460,55 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Описание</t>
+          <t>Цена</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Цена</t>
+          <t>Спектр действия</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Действующее вещество</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Состав</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Действие</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Норма расхода</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Культуры и фазы</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Фасовка</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Физико-химические показатели</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Культура</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Источник описания</t>
         </is>
@@ -478,15 +527,31 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Биоклей для гороха, сои, чечевицы, рапса, льна, горчицы. Предотвращает растрескивание плодов и осыпание зерна</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
           <t>635 ₽/л</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Олигополисахарид бактериального происхождения, гетероферментивные молочнокислые бактерии и комплекс доп. веществ. Предотвращает растрескивание плодов</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Олигополисахарид бактериального происхождения, гетероферментивные молочнокислые бактерии и комплекс доп. веществ. Предотвращает растрескивание плодов</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>1 л/га на 100–200 л воды/га</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>прайс «Сатурн» 2026</t>
         </is>
@@ -505,15 +570,31 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>ПАВ-адъювант для совместного применения с эмульсионными гербицидами. ПАВ-адъювант: снижает поверхностное натяжение раствора, капля растекается и дольше держится на листе, пестицид проникает лучше; расход пестицидов меньше на 10–15%</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
           <t>220 ₽/л</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Этоксилат изодецилового спирта, 900 г/л</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Этоксилат изодецилового спирта, 900 г/л</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>0,2–0,5</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>офсайт: npk-x.ru · прайс «Сатурн» 2026</t>
         </is>
@@ -532,15 +613,31 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Пеногаситель для баковых смесей пестицидов. Кремнийорганические соединения быстро разрушают структуру пены и не дают ей образоваться снова, уменьшают контакт жидкой и газовой фаз, обеспечивают равномерную циркуляцию смеси</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
           <t>по запросу</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Силиконовая эмульсия, функциональные добавки</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Силиконовая эмульсия, функциональные добавки</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,01–0,05</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>офсайт: npk-x.ru · прайс «Сатурн» 2026</t>
         </is>
@@ -559,15 +656,31 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Кондиционер и смягчитель воды под физиологически кислые пестициды. Органические кислоты снижают pH и жёсткость воды, антивспенивающие компоненты образуют плёнку на границе жидкости и воздуха и мешают образованию пузырьков; рабочий pH смеси 5,0–6,0</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
           <t>по запросу</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Ортофосфорная кислота + рН-индикатор</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Ортофосфорная кислота + рН-индикатор</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,1–1</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>офсайт: npk-x.ru · прайс «Сатурн» 2026</t>
         </is>
@@ -586,15 +699,31 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Кремнийорганический ПАВ-адъювант, суперсмачиватель. Смачиватель и пенетрант на гептаметилтрисилоксане: снижает натяжение раствора и усиливает проникновение пестицидов, позволяет сократить расход воды на 30–50%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
           <t>1350 ₽/л</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Гептометилтрисилоксан</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Гептометилтрисилоксан</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,01–0,1</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>офсайт: npk-x.ru · прайс «Сатурн» 2026</t>
         </is>
@@ -613,15 +742,31 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Клей для крестоцветных и зернобобовых — против опадения и потери зерна</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
           <t>по запросу</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Кедровая смола, масло крабе, канифоль, адъюванты</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Кедровая смола, масло крабе, канифоль, адъюванты</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,8–1,5</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>прайс «Сатурн» 2026</t>
         </is>
@@ -640,15 +785,31 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Чистящее средство для промывки опрыскивающего оборудования. Моющее средство для опрыскивателя: комплексоны и ПАВ переводят солевой налёт в раствор и снимают остатки пестицидов с баков, трубопроводов, фильтров и форсунок</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
           <t>426 ₽/л</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Спирты С11-15 вторичные этоксилированные и бутоксилированные, моноэтаноламин, монобутиловый эфир диэтиленгликоля, 1,4-бис(2-этилгексил)сульфосукцинат натрия, изопропиловый спирт</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Спирты С11–15 вторичные этоксилированные и бутоксилированные, моноэтаноламин, монобутиловый эфир диэтиленгликоля, 1,4-бис(2-этилгексил)сульфосукцинат натрия, изопропиловый спирт</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,1–0,3</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>офсайт: npk-x.ru · прайс «Сатурн» 2026</t>
         </is>
@@ -667,15 +828,31 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>ПАВ-адъювант для повышения эффективности СЗР. Рапсовое масло с эмульгаторами: раствор растекается по листу, масляная основа удерживает препарат, замедляет испарение и помогает пройти через кутикулу, стабилизирует баковые смеси</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
           <t>по запросу</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Сложные эфиры жирных кислот, анионные сложных эфиров алкилполигликозида, этоксилированных жирных спиртов и хьюмекантов</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Сложные эфиры жирных кислот, анионные сложных эфиров алкилполигликозида, этоксилированных жирных спиртов и хьюмекантов</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,5–1</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>офсайт: npk-x.ru · прайс «Сатурн» 2026</t>
         </is>
@@ -694,15 +871,35 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>рН-корректор рабочего раствора. Понижает pH рабочего раствора, предотвращает щелочной гидролиз пестицидов, связывает соли жёсткости — кальций, магний, железо, снижает поверхностное натяжение и пенообразование</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
           <t>700 ₽/л</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Подкисляет рабочий раствор, связывает соли жёсткости, снижает поверхностное натяжение</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Подкисляет рабочий раствор, связывает соли жёсткости, снижает поверхностное натяжение</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>30–150 мл на 100 л</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>канистра 10 л</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>офсайт: volskybiochem.com · прайс «Сатурн» 2026</t>
         </is>
@@ -721,15 +918,43 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1040 ₽/л</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>Однолетние и некоторые многолетние двудольные сорняки</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1040 ₽/л</t>
-        </is>
-      </c>
       <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>фомесафен 250 г/л</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1,5–2 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Соя</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>20 л, штабель</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>Соя</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>прайс «Сатурн» 2026</t>
         </is>
@@ -748,15 +973,43 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>540 ₽/л</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>Гербицид сплошного действия</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>540 ₽/л</t>
-        </is>
-      </c>
       <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>глифосат (калийная соль) 540 г/л</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1,4–5 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Пары, поля под посев, земли не с/х</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>20 л, штабель</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница; Ячмень; Рапс; Подсолнечник; Соя; Кукуруза; Горох; Гречиха; Лён; Свёкла; Картофель; Овощи</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>прайс «Сатурн» 2026</t>
         </is>
@@ -775,15 +1028,43 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>по запросу</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>Гербицид сплошного действия</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>по запросу</t>
-        </is>
-      </c>
       <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>глифосат (изопропиламинная соль) 360 г/л</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2–8 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Поля, пары под посев</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>20 л, штабель</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница; Ячмень; Рапс; Подсолнечник; Соя; Кукуруза; Горох; Гречиха; Лён; Свёкла; Картофель; Овощи</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>прайс «Сатурн» 2026</t>
         </is>
@@ -802,15 +1083,43 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2590 ₽/кг</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
           <t>Однолетние двудольные сорняки, в т.ч. устойчивые к 2,4-Д и МЦПА</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>2590 ₽/кг</t>
-        </is>
-      </c>
       <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>трибенурон-метил 750 г/кг</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,01–0,05 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница яровая/озимая, ячмень яровой/озимый, овёс, SU-подсолнечник</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0,5 кг × 10</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница; Ячмень; Подсолнечник</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>прайс «Сатурн» 2026</t>
         </is>
@@ -829,15 +1138,43 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1825 ₽/л</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
           <t>Однолетние двудольные и некоторые однолетние злаковые сорняки</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>1825 ₽/л</t>
-        </is>
-      </c>
       <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>бентазон 360 г/л + ацифлуорфен 80 г/л</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>1–1,5 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Соя</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>5 л × 4</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>Соя</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>прайс «Сатурн» 2026</t>
         </is>
@@ -856,15 +1193,43 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>877,5 ₽/л</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>Однолетние злаковые, многолетние злаковые (пырей ползучий)</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>877,5 ₽/л</t>
-        </is>
-      </c>
       <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>клетодим 240 г/л</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,2–1 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Свёкла сахарная, рапс яровой/озимый, соя, лён, подсолнечник</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>5 л × 4</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>Рапс; Подсолнечник; Соя; Свёкла; Лён</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>прайс «Сатурн» 2026</t>
         </is>
@@ -883,15 +1248,43 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>540 ₽/л</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
           <t>Однолетние двудольные, в т.ч. устойчивые к 2,4-Д и МЦПА, и некоторые многолетние двудольные</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>540 ₽/л</t>
-        </is>
-      </c>
       <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2,4-Д кислоты (2-этилгексиловый эфир) 410 г/л + флорасулам 7,4 г/л</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,3–0,5 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница яровая/озимая, ячмень яровой, кукуруза, просо, сорго</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>10 л × 2</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница; Ячмень; Кукуруза</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>прайс «Сатурн» 2026</t>
         </is>
@@ -910,15 +1303,43 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>4050 ₽/кг</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>Однолетние и некоторые многолетние двудольные, в т.ч. сложноцветные</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>4050 ₽/кг</t>
-        </is>
-      </c>
       <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>клопиралид 750 г/кг</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,12 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Свёкла сахарная, рапс яровой (семена), лён долгунец/масличный</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>1 кг × 10</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>Рапс; Свёкла; Лён</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>прайс «Сатурн» 2026</t>
         </is>
@@ -937,15 +1358,43 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1065 ₽/л</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>Однолетние двудольные и злаковые сорняки</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>1065 ₽/л</t>
-        </is>
-      </c>
       <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>кломазон 480 г/л</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,7–1 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Соя</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>5 л × 4</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>Соя</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>прайс «Сатурн» 2026</t>
         </is>
@@ -964,15 +1413,43 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>880 ₽/л</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
           <t>Однолетние злаковые и двудольные сорняки</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>880 ₽/л</t>
-        </is>
-      </c>
       <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>имазамокс 40 г/л</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,75–1 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Соя, горох и нут (на зерно)</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>5 л × 4</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>Соя; Горох</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>прайс «Сатурн» 2026</t>
         </is>
@@ -991,15 +1468,43 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>1150 ₽/л</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
           <t>Однолетние злаковые и некоторые двудольные сорняки</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>1150 ₽/л</t>
-        </is>
-      </c>
       <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>С-метолахлор 960 г/л</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>1,3–1,6 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Кукуруза, соя, подсолнечник, рапс яровой, свёкла сахарная</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>5 л × 4</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>Рапс; Подсолнечник; Соя; Кукуруза; Свёкла</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>прайс «Сатурн» 2026</t>
         </is>
@@ -1018,15 +1523,43 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>745 ₽/л</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>Однолетние злаковые сорняки</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>745 ₽/л</t>
-        </is>
-      </c>
       <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>феноксапроп-П-этил 69 г/л + антидот клоквинтосет-мексил 34,5 г/л</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,8–1 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница яровая/озимая, ячмень яровой</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>10 л × 2</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница; Ячмень</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t>прайс «Сатурн» 2026</t>
         </is>
@@ -1045,15 +1578,43 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1040 ₽/л</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
           <t>Однолетние двудольные сорняки</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>1040 ₽/л</t>
-        </is>
-      </c>
       <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>бентазон 480 г/л</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>1,5–4 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница яровая/озимая, ячмень яровой/озимый, рожь яровая/озимая, овёс, горох, нут, соя, лён-долгунец</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>20 л, штабель</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница; Ячмень; Соя; Горох; Лён</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>прайс «Сатурн» 2026</t>
         </is>
@@ -1072,15 +1633,43 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>850 ₽/л</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
           <t>Однолетние злаковые, многолетние злаковые (пырей ползучий)</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>850 ₽/л</t>
-        </is>
-      </c>
       <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>галоксифоп-П-метил 108 г/л</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0,5–1 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Рапс яровой/озимый, соя, подсолнечник</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>5 л × 4 · 10 л × 2</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>Рапс; Подсолнечник; Соя</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>прайс «Сатурн» 2026</t>
         </is>
@@ -1099,15 +1688,43 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>5625 ₽/кг</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>Однолетние и некоторые многолетние двудольные, в т.ч. устойчивые к 2,4-Д и МЦПА</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>5625 ₽/кг</t>
-        </is>
-      </c>
       <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>тифенсульфурон-метил 750 г/л</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,006–0,025 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница яровая/озимая, ячмень яровой/озимый, кукуруза (на зерно), соя, лён долгунец/масличный</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>0,1 кг × 100</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница; Ячмень; Соя; Кукуруза; Лён</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
         <is>
           <t>прайс «Сатурн» 2026</t>
         </is>
@@ -1126,15 +1743,43 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>по запросу</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
           <t>Однолетние и некоторые многолетние двудольные сорняки</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>по запросу</t>
-        </is>
-      </c>
       <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>тифенсульфурон-метил 500 г/кг + флорасулам 170 г/кг</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,025–0,035 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Зерновые колосовые яровые/озимые за исключением овса, кукуруза (зерно)</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>0,5 кг</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница; Ячмень; Кукуруза</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>прайс «Сатурн» 2026</t>
         </is>
@@ -1153,15 +1798,43 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>800 ₽/л</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
           <t>Однолетние злаковые (овсюг, метлица обыкновенная, щетинники, мятлик, просовидные)</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>800 ₽/л</t>
-        </is>
-      </c>
       <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>феноксапроп-П-этил 100 г/л + антидот клоквинтосет-мексил 27 г/л</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>0,4–0,9 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница яровая/озимая</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>5 л × 4 · 10 л × 2</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>прайс «Сатурн» 2026</t>
         </is>
@@ -1180,15 +1853,43 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>880 ₽/л</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>Однолетние двудольные сорные растения</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>880 ₽/л</t>
-        </is>
-      </c>
       <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>МЦПА (диметиламинная + натриевая + калиевая соль) 500 г/л</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,5–1,5 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница яровая/озимая, ячмень яровой/озимый, рожь озимая, овёс, горох (на зерно), картофель, лён-долгунец</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>10 л × 2</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница; Ячмень; Картофель; Горох; Лён</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
         <is>
           <t>прайс «Сатурн» 2026</t>
         </is>
@@ -1207,15 +1908,43 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>945 ₽/л</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
           <t>Однолетние злаковые и двудольные и некоторые многолетние сорняки</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>945 ₽/л</t>
-        </is>
-      </c>
       <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>имазамокс 33 г/л + имазапир 15 г/л</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>1–1,2 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Подсолнечник (на масло и зерно), устойчивый к имидазолинонам</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>5 л × 4 · 10 л × 2</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>Подсолнечник</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>прайс «Сатурн» 2026</t>
         </is>
@@ -1234,15 +1963,43 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>392 ₽/л</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
           <t>Десикация</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>392 ₽/л</t>
-        </is>
-      </c>
       <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>дикват дибромид 150 г/л (пересчёт на дикват-ион 80,3 г/л)</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>2 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Подсолнечник</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>10 л × 2</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>Подсолнечник</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>прайс «Сатурн» 2026</t>
         </is>
@@ -1261,15 +2018,43 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>540 ₽/л</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
           <t>Десикация</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>540 ₽/л</t>
-        </is>
-      </c>
       <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>дикват дибромид 240 г/л (пересчёт на дикват-ион 128 г/л)</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>0,7–1,8 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Подсолнечник, соя, рапс яровой, горох, картофель</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>10 л × 2</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>Рапс; Подсолнечник; Соя; Картофель; Горох</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
         <is>
           <t>прайс «Сатурн» 2026</t>
         </is>
@@ -1288,15 +2073,43 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Клоп вредная черепашка, блошки, тли, цикадки, трипсы, пьявица, рапсовый цветоед, крестоцветные блошки, свекловичная листовая тля и минирующая муха, гороховая зерновка и плодожорка, долгоносики, саранчовые</t>
+          <t>510 ₽/л</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>510 ₽/л</t>
+          <t>Клоп вредная черепашка, блошки, тли, цикадки, трипсы, пьявица, рапсовый цветоед, крестоцветные блошки, свекловичная листовая тля и минирующая муха, гороховая зерновка и плодожорка, долгоносики, саранч</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>альфа-циперметрин 100 г/л</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>0,1–0,3 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница яровая/озимая, ячмень яровой/озимый, рапс яровой/озимый, картофель, свёкла кормовая и сахарная, горох, люцерна, участки, заселённые саранчовыми</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>5 л × 4 · 10 л × 2</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница; Ячмень; Рапс; Картофель; Свёкла; Горох</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
         <is>
           <t>прайс «Сатурн» 2026</t>
         </is>
@@ -1315,15 +2128,43 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Клоп вредная черепашка, хлебные жуки и блошки, пшеничные трипсы, тли, внутристеблевые мухи, пьявица, стеблевые пилильщики, свекловичные долгоносики, луговой мотылёк, гороховая зерновка и плодожорка, бобовая огнёвка, соевая плодожорка, клубеньковый долгоносик, рапсовый цветоед и пилильщик</t>
+          <t>1150 ₽/л</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1150 ₽/л</t>
+          <t>Клоп вредная черепашка, хлебные жуки и блошки, пшеничные трипсы, тли, внутристеблевые мухи, пьявица, стеблевые пилильщики, свекловичные долгоносики, луговой мотылёк, гороховая зерновка и плодожорка, б</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>ацетамиприд 115 г/л + лямбда-цигалотрин 106 г/л</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>0,1–0,5 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница яровая/озимая, ячмень яровой, свёкла сахарная, горох, нут, соя, рапс яровой</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>5 л × 4</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница; Ячмень; Рапс; Соя; Свёкла; Горох</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
         <is>
           <t>прайс «Сатурн» 2026</t>
         </is>
@@ -1342,15 +2183,43 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Клубеньковый долгоносик, многоягодные совки, бобовая огнёвка, крестоцветные блошки, рапсовый пилильщик и цветоед, рапсовый семенной скрытнохоботник, клоп вредная черепашка, тли, хлебные жуки, пшеничный трипс, хлебные блошки, пьявицы</t>
+          <t>1125 ₽/л</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>1125 ₽/л</t>
+          <t>Клубеньковый долгоносик, многоягодные совки, бобовая огнёвка, крестоцветные блошки, рапсовый пилильщик и цветоед, рапсовый семенной скрытнохоботник, клоп вредная черепашка, тли, хлебные жуки, пшеничны</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>клотианидин 140 г/л + лямбда-цигалотрин 100 г/л</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>0,1–0,25 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Зерновые колосовые (кроме овса), рапс яровой/озимый, соя</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>5 л × 4</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница; Ячмень; Рапс; Соя</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
         <is>
           <t>прайс «Сатурн» 2026</t>
         </is>
@@ -1369,15 +2238,43 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>1040 ₽/л</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
           <t>Хлебная жужелица, клоп вредная черепашка, хлебные жуки, злаковые тли, пьявицы, крестоцветные блошки</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>1040 ₽/л</t>
-        </is>
-      </c>
       <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>клотианидин 140 г/л + лямбда-цигалотрин 100 г/л</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>0,5–1 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница яровая/озимая, ячмень, рапс</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>5 л × 4 · 10 л × 2</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница; Ячмень; Рапс</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
         <is>
           <t>прайс «Сатурн» 2026</t>
         </is>
@@ -1396,15 +2293,43 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Борное микроудобрение для цветения, опыления и формирования завязей. Бор в органической форме с мембранным проникателем: деление клеток и построение клеточных стенок, рост пыльцевых трубок и оплодотворение завязи, отток продуктов фотосинтеза в клубни и корнеплоды</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
           <t>760 ₽/л</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr"/>
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Бор 131 г/л (13,1%) · N 60 г/л (6%) · органический проникатель</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>0,5–1,0 л/га</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Подсолнечник (формирование корзинки), сах. свёкла (перед смыканием рядков), картофель (смыкание рядков), горох/соя/рапс/горчица (бутонизация, перед цветением)</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>канистра 10 л</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>Плотность 1,3 г/см³</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>Рапс; Подсолнечник; Соя; Картофель; Свёкла; Горох</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
         <is>
           <t>офсайт: volskybiochem.com · каталог производителя</t>
         </is>
@@ -1423,15 +2348,43 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Хелатное железосодержащее микроудобрение для профилактики хлороза. Железо в хелате ОЭДФ: образование хлорофилла и усиление фотосинтеза, белковый обмен и синтез ауксинов, устранение хлороза от нехватки железа</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
           <t>430 ₽/л</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr"/>
+      <c r="E37" s="2" t="inlineStr"/>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Железо 100 г/л (10%) · N 41 г/л (4,1%) · органический мембранный проникатель</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Овощные и плодово-ягодные 0,5–1,0 л/га (1–3 обработки), зерновые 0,5 л/га (1 обработка). Рабочий раствор 100–300 л/га</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Овощные, зерновые, плодово-ягодные — при хлорозе и недостатке железа</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>канистра 10 л</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>Плотность 1,3 г/см³</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница; Ячмень; Овощи</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
         <is>
           <t>офсайт: volskybiochem.com · каталог производителя</t>
         </is>
@@ -1450,15 +2403,43 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Хелатное медное микроудобрение для обменных процессов и устойчивости. Медь в хелате ОЭДФ участвует в синтезе окислительно-восстановительных ферментов, усиливает фотосинтез и дыхание, повышает устойчивость злаковых к полеганию и грибным болезням</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
           <t>465 ₽/л</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Медь 82 г/л (8,2%) · N 41 г/л (4,1%) · органический мембранный проникатель</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>0,2–1,0 л/га</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Культуры при недостатке меди</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>канистра 10 л</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>Плотность 1,2 г/см³</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница; Ячмень; Рапс; Подсолнечник; Соя; Кукуруза; Горох; Гречиха; Лён; Свёкла; Картофель; Овощи</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
         <is>
           <t>офсайт: volskybiochem.com · каталог производителя</t>
         </is>
@@ -1477,15 +2458,43 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Высококонцентрированное серное удобрение для серолюбивых культур. Сера входит в состав белков и ферментов, улучшает усвоение азота из почвы; магний усиливает углеводный и липидный обмен. Повышает белок и клейковину у зерновых, масличность у рапса и горчицы</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
           <t>490 ₽/л</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr"/>
+      <c r="E39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Сера 72% · N 27 г/л (2,7%) · Mg 31 г/л (3,1%)</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>0,5–1,0 л/га (до 1 л/га при низком содержании серы). Рабочий раствор 100–300 л/га</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Рапс, сурепица, рыжик (3–7 лист — розетка) · горох, соя, нут (3–4 лист — стеблевание) · зерновые (колошение — флаговый лист)</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>канистра 10 л</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>Плотность 1,4 г/см³</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница; Ячмень; Рапс; Соя; Горох</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
         <is>
           <t>офсайт: volskybiochem.com · каталог производителя</t>
         </is>
@@ -1504,15 +2513,43 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Цинковое микроудобрение для роста, фотосинтеза и стрессоустойчивости. Цинк в хелате ЭДТА улучшает усвоение фосфора, активирует ферменты, регулирует корнеобразование и накопление фитогормонов; влагоудерживающая добавка повышает засухоустойчивость</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
           <t>728 ₽/л</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr"/>
+      <c r="E40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Цинк 75 г/л (7,5%) · N 41 г/л (4,1%) · влагоудерживающий компонент</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>0,5 л/га, 1 обработка (до 1 л/га при низком содержании цинка). Рабочий раствор 100–300 л/га</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Кукуруза (5–9 лист) · другие культуры — рост листьев и стеблей</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>канистра 10 л</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>Плотность 1,2 г/см³</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>Кукуруза</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
         <is>
           <t>офсайт: volskybiochem.com · каталог производителя</t>
         </is>
@@ -1531,15 +2568,43 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Микроудобрение с бором и молибденом для цветения и азотного обмена. Бор и молибден в органической форме с мембранным проникателем: молибден улучшает усвоение азота и работу клубеньковых бактерий, бор улучшает опыление и оплодотворение цветков</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
           <t>1290 ₽/л</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr"/>
+      <c r="E41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Бор 100 г/л (10%) · Молибден 40 г/л (4%) · N 70 г/л (7%) · мембранный проникатель. Самое высокое содержание молибдена в линейке</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Семена 0,5–1,0 л/т · листовая подкормка 0,5–1,5 л/га</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Зернобобовые — горох, соя, нут, чечевица · семенники многолетних трав, лён</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>канистра 10 л</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>Плотность 1,4 г/см³</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>Соя; Горох; Лён</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
         <is>
           <t>офсайт: volskybiochem.com · каталог производителя</t>
         </is>
@@ -1558,15 +2623,43 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Удобрение с кальцием и азотом для прочности тканей и качества плодов. Кальций в хелате ЭДТА укрепляет кутикулу и клеточные стенки, поддерживает кислотно-щелочное равновесие и синтез хлорофилла, снижает вершинную гниль и растрескивание плодов, повышает лёжкость</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
           <t>650 ₽/л</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr"/>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Кальций 100 г/л (10%) · Азот 50 г/л (5%)</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>0,5–2,0 л/га, листовая подкормка</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Плодово-ягодные, овощи, картофель</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>канистра 10 л</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>Плотность 1,2 г/см³</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>Картофель; Овощи</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
         <is>
           <t>офсайт: volskybiochem.com · каталог производителя</t>
         </is>
@@ -1585,15 +2678,39 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Микроудобрение с кобальтом и селеном для азотфиксации и антистрессовой защиты. Кобальт в хелате ОЭДФ и селен: антиоксидантное действие, связывание токсичных веществ, устойчивость клеточных мембран, лучшее усвоение макро- и микроэлементов, обогащение кормов</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
           <t>1020 ₽/л</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr"/>
+      <c r="E43" s="2" t="inlineStr"/>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Кобальт 50 г/л (5%) · Селен 1 г/л (0,1%) · Азот 10 г/л (1%) · Сера 70 г/л (7%) · Фосфор 13 г/л (1,3%)</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>0,5–1,0 л/га, листовая подкормка</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>Многолетние травы (клевер, люцерна, козлятник и смеси со злаковыми), кормовые культуры</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>канистра 10 л</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>Плотность 1,1 г/см³</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
         <is>
           <t>офсайт: volskybiochem.com · каталог производителя</t>
         </is>
@@ -1612,15 +2729,43 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Удобрение с кремнием и калием для прочности тканей и стрессоустойчивости. Кремний с калием укрепляют клеточные стенки, ускоряют синтез антиоксидантных ферментов, снижают транспирацию при засухе и токсичность избытка железа и алюминия</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
           <t>695 ₽/л</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Кремний 340 г/л (34%) · Калий 160 г/л (16%) · Азот 2,3 г/л (0,23%), амидная форма</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Семена 0,2–0,5 л/т · листовая подкормка 0,2–1,0 л/га</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Зерновые, плодово-ягодные, овощи</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>канистра 10 л</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>Плотность 1,3 г/см³</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница; Ячмень; Овощи</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
         <is>
           <t>офсайт: volskybiochem.com · каталог производителя</t>
         </is>
@@ -1639,15 +2784,43 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Микроудобрение с магнием и марганцем для фотосинтеза и ферментативных процессов. Магний и марганец в хелате ОЭДФ усиливают фотосинтез и накопление сухого вещества, устраняют хлорозы; влагоудерживающая добавка снижает испарение раствора и повышает засухоустойчивость</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
           <t>520 ₽/л</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr"/>
+      <c r="E45" s="2" t="inlineStr"/>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Магний 50 г/л (5%) · Марганец 10 г/л (1%) · Азот 10 г/л (1%) · Сера 110 г/л (11%) · Фосфор 36 г/л (3,6%)</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>0,5–2,0 л/га, листовая подкормка</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Плодово-ягодные, сахарная свёкла, кукуруза</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>канистра 10 л</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>Плотность 1,2 г/см³</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>Кукуруза; Свёкла</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
         <is>
           <t>офсайт: volskybiochem.com · каталог производителя</t>
         </is>
@@ -1666,15 +2839,43 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Микроудобрение с магнием и цинком для фотосинтеза и стрессоустойчивости. Магний в хелате ОЭДФ усиливает синтез хлорофилла и ауксинов, стабилизирует дыхание и обмен углеводов, повышает устойчивость к жаре, засухе и морозу; с цинком действуют синергично</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
           <t>653 ₽/л</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr"/>
+      <c r="E46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Магний 75 г/л (7,5%) · Цинк 30 г/л (3%) · Азот 52 г/л (5,2%) · Сера 37 г/л (3,7%) · Фосфор 14 г/л (1,4%) · хелат ОЭДФ. Самое высокое содержание магния</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>0,5–2,0 л/га, листовая подкормка</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Кукуруза, сахарная свёкла, картофель, овощи, плодово-ягодные</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>канистра 10 л</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>Плотность 1,2 г/см³</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>Кукуруза; Картофель; Свёкла; Овощи</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
         <is>
           <t>офсайт: volskybiochem.com · каталог производителя</t>
         </is>
@@ -1693,15 +2894,43 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Микроудобрение с марганцем и бором для цветения и формирования урожая. Марганец в хелате ОЭДФ с мембранным проникателем усиливает окислительно-восстановительные реакции и отток пластических веществ, стимулирует синтез предшественников фитогормонов</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
           <t>1290 ₽</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr"/>
+      <c r="E47" s="2" t="inlineStr"/>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Марганец 50 г/л (5%) · Бор 25 г/л (2,5%) · Азот 25 г/л (2,5%)</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>0,5–2,0 л/га, листовая подкормка</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Плодово-ягодные, овощи, картофель, сахарная свёкла, подсолнечник</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>канистра 10 л</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>Плотность 1,2 г/см³</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>Подсолнечник; Картофель; Свёкла; Овощи</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
         <is>
           <t>офсайт: volskybiochem.com · каталог производителя</t>
         </is>
@@ -1720,15 +2949,43 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Микроудобрение с марганцем и цинком для роста и фотосинтеза. Марганец и цинк в хелате ОЭДФ усиливают окислительно-восстановительные реакции и синтез фитогормонов; влагоудерживающая добавка повышает засухо- и жароустойчивость</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
           <t>605 ₽/л</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr"/>
+      <c r="E48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Марганец 56 г/л (5,6%) · Цинк 28 г/л (2,8%) · Азот 10 г/л (1%) · Сера 120 г/л (12%) · Фосфор 6 г/л (0,6%) · хелат ОЭДФ</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>0,5–2,0 л/га, листовая подкормка</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Плодово-ягодные, овощи, картофель, кукуруза, сахарная свёкла</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>канистра 10 л</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>Плотность 1,2 г/см³</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>Кукуруза; Картофель; Свёкла; Овощи</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
         <is>
           <t>офсайт: volskybiochem.com · каталог производителя</t>
         </is>
@@ -1747,15 +3004,43 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Специализированное микроудобрение для питания пивоваренного ячменя. Ограничивает азотфиксацию, препятствует избыточному накоплению белка, стимулирует фотосинтез и накопление углеводов</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
           <t>651 ₽</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr"/>
+      <c r="E49" s="2" t="inlineStr"/>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Состав линейки «Микроэл», вариант для пивоваренного ячменя: ограничивает азотфиксацию, препятствует избыточному накоплению белка, стимулирует фотосинтез и накопление углеводов</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>0,2–0,4 л/га, 2 обработки. Рабочий раствор 30–300 л/га</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Пивоваренный ячмень</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>канистра 10 л</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>Плотность 1,3 г/см³</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>Ячмень</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
         <is>
           <t>офсайт: volskybiochem.com · каталог производителя</t>
         </is>
@@ -1774,15 +3059,43 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Комплексное микроудобрение для листовых подкормок и коррекции дефицитов. 4 макро- и 11 микроэлементов в хелатной форме: стимулирует фотосинтез и азотфиксацию, помогает переносить стресс от гербицидов, засухи и заморозков, повышает клейковину пшеницы</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
           <t>651 ₽/л</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr"/>
+      <c r="E50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Mn 3,4 · Mo 2,2 · MgO 15 · Zn 14 · Cu 6 · Fe 3,0 · Co 0,8 · B 1,6 · SO3 68 · N 4 · K2O 0,3 г/л · + Cr, Ni, Li, Se. 15 элементов, микро — хелат ЭДТА</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>0,2–0,5 л/га, 2 обработки (при однократной — до 0,4 л/га). Рабочий раствор 30–300 л/га</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Кукуруза 0,2 (5–9 лист, трубкование), подсолнечник 0,2, сах. свёкла 0,4, зернобобовые 0,2, озимые и яровые зерновые 0,2 (кущение, колошение), картофель 0,4, плодово-ягодные 0,5–1,0</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>канистра 10 л</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>Плотность 1,3 г/см³</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница; Ячмень; Подсолнечник; Кукуруза; Картофель; Свёкла</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
         <is>
           <t>офсайт: volskybiochem.com · каталог производителя</t>
         </is>
@@ -1801,15 +3114,43 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Борное микроудобрение для цветения, опыления и формирования плодов. Бор в органической форме: рост пыльцевых трубок и завязываемость плодов, углеводный и белковый обмен, регуляция ауксинов, лёжкость корнеплодов, баланс питания кальцием</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
           <t>765 ₽/л</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr"/>
+      <c r="E51" s="2" t="inlineStr"/>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Бор (B) 130–150 г/л (в соединении с этаноламином ≥460 г/л) · азот (N) 90–110 г/л · молибден (MoO3) 4–8 г/л · рН 8–9,5</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>0,5–1,5 л/га листовая подкормка</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Все сельхозкультуры. Подсолнечник (2–5 пар листьев, начало образования корзинки), сахарная свёкла 1,0–1,5 л/га</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>раствор</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>рН 8–9,5</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница; Ячмень; Рапс; Подсолнечник; Соя; Кукуруза; Горох; Гречиха; Лён; Свёкла; Картофель; Овощи</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
         <is>
           <t>офсайт: relict-dv.ru · каталог производителя</t>
         </is>
@@ -1828,15 +3169,43 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Кремниевое удобрение с калием для укрепления растений и стрессоустойчивости. Кремний с калием укрепляют стебель и снижают полегание, улучшают фотосинтез и усвоение азота, калия, кальция и магния, повышают устойчивость к засухе, заморозкам и грибным инфекциям</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
           <t>470 ₽/л</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr"/>
+      <c r="E52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Кремний (SiO2) 210–230 г/л · Калий (K2O) 90–110 г/л · рН 11–12</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>0,2 л/га, до 3 обработок за вегетацию</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>Все сельхозкультуры. Зерновые — снижение риска полегания · томаты (подтверждено)</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>раствор</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>рН 11–12</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница; Ячмень; Рапс; Подсолнечник; Соя; Кукуруза; Горох; Гречиха; Лён; Свёкла; Картофель; Овощи</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
         <is>
           <t>офсайт: relict-dv.ru · каталог производителя</t>
         </is>
@@ -1855,15 +3224,43 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Молибденовое микроудобрение с аминокислотами для азотного обмена. Молибден с аминокислотами: стимулирует клубеньковые бактерии и фиксацию азота, помогает синтезу белка и его качеству в семенах, улучшает поглощение фосфора</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
           <t>1340 ₽/л</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr"/>
+      <c r="E53" s="2" t="inlineStr"/>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Молибден (MoO3) 60–70 г/л · азот (N) 25–35 г/л · комплекс аминокислот 100–120 г/л · рН 8–9,5</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>Обработка семян 0,5 л/т · листовая подкормка 0,2–0,4 л/га</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>Бобовые (ключевая роль в усвоении азота), соя, клевер · все сельхозкультуры</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>раствор</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>рН 8–9,5</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница; Ячмень; Рапс; Подсолнечник; Соя; Кукуруза; Горох; Гречиха; Лён; Свёкла; Картофель; Овощи</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
         <is>
           <t>офсайт: relict-dv.ru · каталог производителя</t>
         </is>
@@ -1882,15 +3279,43 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Серное удобрение для синтеза аминокислот, белка и повышения урожайности. Сера участвует в образовании белков, ферментов и эфирных масел, улучшает усвоение азота, повышает качество зерна злаковых и содержание незаменимых аминокислот в кормовых культурах</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
           <t>730 ₽/л</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr"/>
+      <c r="E54" s="2" t="inlineStr"/>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Сера (SO3) 550–600 г/л · азот (N) 110–130 г/л · рН 5–6. Сульфитная форма</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>0,3–1,5 л/га</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>Рапс, соя, капуста и другие серолюбивые культуры · зерновые — качество зерна</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>раствор</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>рН 5–6</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница; Ячмень; Рапс; Соя</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
         <is>
           <t>офсайт: relict-dv.ru · каталог производителя</t>
         </is>
@@ -1909,15 +3334,43 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Цинковое удобрение с аминокислотами для фотосинтеза и качества урожая. Цинк с аминокислотами: синтез белков, витаминов и ауксинов, обмен углеводов и фосфора, завязывание и форма плодов, защита белков и липидов от окисления, водоудерживающая способность клеток</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
           <t>695 ₽/л</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr"/>
+      <c r="E55" s="2" t="inlineStr"/>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Цинк (ZnO) 120–140 г/л · азот (N) 30–40 г/л · комплекс аминокислот 15–180 г/л · рН 5–6</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>0,3–1,5 л/га</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>Кукуруза (3–5 лист, 4 лист при гербицидной обработке) · все сельхозкультуры</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>раствор</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>рН 5–6</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница; Ячмень; Рапс; Подсолнечник; Соя; Кукуруза; Горох; Гречиха; Лён; Свёкла; Картофель; Овощи</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
         <is>
           <t>офсайт: relict-dv.ru · каталог производителя</t>
         </is>
@@ -1936,15 +3389,39 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Гуминово-фульвовый стимулятор для повышения урожайности и стрессоустойчивости. Соли гуминовых и фульвовых кислот: улучшают питание проростка, усиливают иммунный ответ на почвенные патогены, повышают содержание хлорофилла, снижают вред от засухи и гербицидного стресса</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
           <t>615 ₽/л</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr"/>
+      <c r="E56" s="2" t="inlineStr"/>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Соли гуминовых и фульвовых кислот 4–6% (40–60 г/л) · N общий 0,2–0,5% · N аммонийный 0,1–0,25% · P общий 0,2–0,35% · K общий 0,2–0,35% · рН 9,0–11</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>Обработка семян 0,4 л/т · листовые подкормки — по схеме, часто в баковой смеси с «Реликт М»</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>Все сельхозкультуры. Подтверждено на клевере, яровом рапсе, кукурузе</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>Жидкость, рН 9,0–11</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница; Ячмень; Рапс; Подсолнечник; Соя; Кукуруза; Горох; Гречиха; Лён; Свёкла; Картофель; Овощи</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
         <is>
           <t>офсайт: relict-dv.ru · каталог производителя</t>
         </is>
@@ -1963,15 +3440,43 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Жидкое калийное удобрение для качества и лёжкости урожая. Калий 152 г/л с микроэлементами и кремнием: участвует в синтезе углеводов и их оттоке из листьев в семена, клубни и плоды; смачиватель и прилипатель удерживают раствор на листе</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
           <t>332,5 ₽/л</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr"/>
+      <c r="E57" s="2" t="inlineStr"/>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>K2O 152 · N 51 · P2O5 63 · SO3 44,2 · Fe 0,25 · Mn 2,4 · B 0,11 · Zn 0,063 · Cu 0,063 · Mo 0,013 · Co 0,013 · Se 0,013 г/л. 12 элементов питания</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>3–5 л/га (стандарт 3 л/га). Рабочий раствор 100–300 л/га</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>Кукуруза (трубкование), подсолнечник (формирование корзинки), сах. свёкла, зернобобовые (бутонизация), рис, картофель (после цветения)</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>канистра 10 л, флакон 0,9 л</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>Плотность 1,3 г/см³</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>Подсолнечник; Кукуруза; Картофель; Свёкла</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
         <is>
           <t>офсайт: volskybiochem.com · каталог производителя</t>
         </is>
@@ -1990,15 +3495,43 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Жидкое азотное удобрение с микроэлементами для роста вегетативной массы. Азот в трёх формах и хелаты микроэлементов с проникающим агентом: ускоряет перевод азота в органическую форму, усиливает синтез аминокислот и белков, кремний укрепляет соломину против полегания</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
           <t>409,5 ₽/л</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr"/>
+      <c r="E58" s="2" t="inlineStr"/>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>N 374 · P2O5 28 · K2O 42 · MgO 2,1 · SO3 17,5 · Fe 0,42 · Mn 0,7 · B 0,22 · Zn 1,8 · Cu 0,83 · Mo 0,7 · Co 0,014 · Se 0,014 г/л · + органические кислоты, витамины, кремний</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>3–5 л/га (стандарт 3 л/га). Рабочий раствор 100–300 л/га</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>Кукуруза (5–9 лист, трубкование), подсолнечник (4–5 пар листьев), сах. свёкла, зернобобовые, озимые и яровые зерновые (кущение, колошение), картофель</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>канистра 10 л, флакон 0,9 л</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>Суспензия, 374 г/л азота</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница; Ячмень; Подсолнечник; Кукуруза; Картофель; Свёкла</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
         <is>
           <t>офсайт: volskybiochem.com · каталог производителя</t>
         </is>
@@ -2017,15 +3550,43 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Жидкое фосфорное удобрение для развития корней, цветения и плодоношения. Фосфор 258 г/л с микроэлементами: входит в состав АТФ и фитина, кремний повышает доступность фосфора, стимулирует цветение, опыление и созревание, развивает корневую систему</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
           <t>577,5 ₽/л</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr"/>
+      <c r="E59" s="2" t="inlineStr"/>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>N 65 · P2O5 258 · K2O 65 · MgO 2,3 · SO3 10,3 · Fe 0,9 · Mn 0,65 · B 0,26 · Zn 2,1 · Cu 0,9 · Mo 0,65 · Co 0,13 · Se 0,026 г/л</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>3–5 л/га (стандарт 3 л/га) · картофель 5 л/га при обработке клубней. Рабочий раствор 100–300 л/га</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>Кукуруза (5–7 лист), подсолнечник, сах. свёкла, зернобобовые, зерновые (кущение — колошение), картофель</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>канистра 10 л, флакон 0,9 л</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>Стимулирует развитие корневой системы</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница; Ячмень; Подсолнечник; Кукуруза; Картофель; Свёкла</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
         <is>
           <t>офсайт: volskybiochem.com · каталог производителя</t>
         </is>
@@ -2044,15 +3605,43 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Комплексное микроудобрение для обработки семян, повышения всхожести и развития корней. Подаёт микроэлементы на ранних стадиях, когда растение уязвимо: повышает всасывающую способность корней и активность ферментов зародыша; ванадий в составе — катализатор азотфиксации</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
           <t>645,7 ₽/л</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr"/>
+      <c r="E60" s="2" t="inlineStr"/>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>17 элементов питания: 5 макро- и 12 микроэлементов в хелатной форме (в т.ч. ванадий — катализатор азотфиксации). 23 индивидуальных состава под конкретные культуры</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>Семена 2 л/т (1 л состава А + 1 л состава Б), рабочий раствор 10 л/т · клубни 0,5 л/т, рабочий раствор 30 л/т</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>Обработка семян всех полевых культур</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>канистра 10 л</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>Плотность 1,3 г/см³</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница; Ячмень; Рапс; Подсолнечник; Соя; Кукуруза; Горох; Гречиха; Лён; Свёкла; Картофель; Овощи</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
         <is>
           <t>офсайт: volskybiochem.com · каталог производителя</t>
         </is>
@@ -2071,15 +3660,35 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Гуминовый препарат с микроэлементами и Bacillus для предпосевной обработки семян. Соли гуминовых и фульвовых кислот для предпосевной обработки: стимулируют прорастание и рост корней, активизируют почвенные микроорганизмы, сдерживающие почвенно-семенные инфекции</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
           <t>735 ₽/л</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr"/>
+      <c r="E61" s="2" t="inlineStr"/>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>Гуминовые и фульвокислоты 4–6% · хелатные микроэлементы (Mg, Fe, Mn, Cu, Zn) ≥0,4% · консорциум 4 штаммов рода Bacillus, титр ≥1×10⁷</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>Предпосевная обработка семян зерновых колосовых, обработка клубней и посадочного материала · возможны листовые обработки в вегетацию</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница, ячмень, рожь, картофель. Пролонгированная защита от корневых гнилей злаковых и ризоктониоза картофеля</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница; Ячмень; Картофель</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
         <is>
           <t>офсайт: relictorganics.com · каталог производителя</t>
         </is>
@@ -2098,15 +3707,43 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Стартовое микроудобрение для обработки семян и повышения устойчивости всходов. Полимерная композиция закрепляет препарат на семенах, осмотически активные вещества ускоряют поступление элементов и влаги внутрь: всходы дружнее, корни мощнее, прорастание шире по температуре</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
           <t>724,5 ₽/л</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr"/>
+      <c r="E62" s="2" t="inlineStr"/>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>N 2,4 · P2O5 0,61 · K2O 1,77 · MgO 0,97 · SO3 4,9 · Fe 0,35 · Mn 0,58 · B 0,35 · Zn 0,98 · Cu 0,97 · Mo 0,09 · Co 0,18 (% мас.) · микро — хелат ОЭДФ. 12 элементов + полимерные прилипатели</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>Семена 0,5 л/т (рабочий раствор 10 л/т) · клубни 0,2 л/т (рабочий раствор 30 л/т)</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>Предпосевная обработка семян и клубней</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>канистра 10 л</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>Плотность 1,2 г/см³</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница; Ячмень; Рапс; Подсолнечник; Соя; Кукуруза; Горох; Гречиха; Лён; Свёкла; Картофель; Овощи</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
         <is>
           <t>офсайт: volskybiochem.com · каталог производителя</t>
         </is>
@@ -2125,15 +3762,43 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
+          <t>1475 ₽/л</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
           <t>Твёрдая и пыльная головня, фузариозная и гельминтоспориозная корневые гнили, плесневение семян</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>1475 ₽/л</t>
-        </is>
-      </c>
       <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>тиабендазол 60 г/л + тебуконазол 60 г/л + имазалил 40 г/л</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr"/>
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>0,4–0,5 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница яровая/озимая, ячмень яровой/озимый</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>5 л × 4</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница; Ячмень</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
         <is>
           <t>прайс «Сатурн» 2026</t>
         </is>
@@ -2152,15 +3817,43 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
+          <t>945 ₽/л</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
           <t>Хлебная жужелица, внутристеблевые мухи, блошки, тли, цикадки</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>945 ₽/л</t>
-        </is>
-      </c>
       <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>тиаметоксам 350 г/л</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr"/>
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>0,5–1 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница яровая/озимая, ячмень яровой/озимый</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>5 л × 4</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница; Ячмень</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
         <is>
           <t>прайс «Сатурн» 2026</t>
         </is>
@@ -2179,15 +3872,43 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
+          <t>по запросу</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
           <t>Хлебная жужелица, внутристеблевые мухи, блошки, тли, цикадки, проволочник, клубеньковый долгоносик</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>по запросу</t>
-        </is>
-      </c>
       <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>тиаметоксам 350 г/л</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr"/>
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>0,5–9 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница яровая/озимая, ячмень яровой/озимый, рожь озимая, подсолнечник, кукуруза, горох, соя, рапс</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>5 л × 4</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница; Ячмень; Рапс; Подсолнечник; Соя; Кукуруза; Горох</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
         <is>
           <t>прайс «Сатурн» 2026</t>
         </is>
@@ -2206,15 +3927,43 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
+          <t>1760 ₽/л</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
           <t>Проволочники и ложнопроволочники, внутристеблевые мухи, крестоцветные блошки, хлебная жужелица</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>1760 ₽/л</t>
-        </is>
-      </c>
       <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>имидаклоприд 600 г/л</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr"/>
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>0,3–12 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница яровая/озимая, ячмень, рапс, кукуруза, подсолнечник</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>5 л × 4</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница; Ячмень; Рапс; Подсолнечник; Кукуруза</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
         <is>
           <t>прайс «Сатурн» 2026</t>
         </is>
@@ -2233,15 +3982,39 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Гранулированное удобрение для густого газона и ярко-зелёной окраски травы. Быстро растворимые гранулы без пыли: ускоряет отрастание трав после скашивания, повышает густоту травостоя, препятствует мху и сорнякам, даёт ярко-зелёную окраску</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
           <t>96 ₽/кг</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="D67" s="2" t="inlineStr"/>
+      <c r="E67" s="2" t="inlineStr"/>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>N 11 · P2O5 12 · K2O 26 · Ca 0,55 · MgO 0,4 · SO3 0,7 · B 0,09 · Cu 0,08 · Fe 0,16 · Mn 0,16 · Mo 0,008 · Zn 0,09 (%)</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>Закладка газона 10 кг/100 м² · весенняя подкормка 4–5 кг/100 м² · в вегетацию 5–7 кг/100 м²</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>Газон</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>МКР 800 кг / мешки 40 кг</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>Гранулированное</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
         <is>
           <t>каталог производителя</t>
         </is>
@@ -2260,15 +4033,35 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Гранулированное осеннее удобрение для газона. Осенняя подкормка газона: повышенные фосфор и калий обеспечивают укоренение травосмесей, формирование корневой системы и лучшую перезимовку; азот осенью не разгоняет рост под заморозки</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
           <t>97 ₽/кг</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr"/>
+      <c r="E68" s="2" t="inlineStr"/>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>NPK 6:13:36 + микроэлементы — Ca, MgO, SO3, B, Cu, Fe, Mn, Mo, Zn</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>Закладка газона 10 кг/100 м² · по вегетации 7 кг/100 м²</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>Газон</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>водорастворимые гранулы, 800 кг</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
         <is>
           <t>офсайт: fertika.com · прайс «Сатурн» 2026</t>
         </is>
@@ -2287,15 +4080,43 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Специализированное удобрение для клубнеобразования и повышения качества картофеля. Состав подобран под картофель: стимулирует клубнеобразование, не приводит к накоплению нитратов, калий улучшает лёжкость клубней, сера и магний увеличивают их количество</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
           <t>110 ₽/кг</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr"/>
+      <c r="E69" s="2" t="inlineStr"/>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>N 11 · P2O5 9 · K2O 16 · Ca 0,55 · MgO 1 · SO3 4 · B 0,09 · Cu 0,08 · Mn 0,16 (%)</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>Картофель 600–800 кг/га</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>Картофель</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>МКР 800 кг / мешки 40 кг</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>Без хлора</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>Картофель</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
         <is>
           <t>каталог производителя</t>
         </is>
@@ -2314,15 +4135,43 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Высококалийное водорастворимое удобрение для формирования и качества урожая. Повышенный калий на завершающих стадиях: интенсивное плодоношение и равномерное созревание, накопление сахаров, крахмала и белка, оптимизация водного режима и устойчивость к засухе</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
           <t>222 ₽/кг</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr"/>
+      <c r="E70" s="2" t="inlineStr"/>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>N 10,1 · P2O5 5 · K2O 40 · MgO 0,5 · S 4,4 · B 0,03 · Cu 0,01 · Fe 0,15 · Mn 0,14 · Mo 0,003 · Zn 0,01 (%)</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>Некорневая подкормка 2–5 кг/га. Фертигация: теплицы 0,05–0,2%, открытый грунт 0,1–0,2%</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>Масличные (бутонизация), зерновые (флаговый лист — колошение), картофель (рост клубней), виноград 2–5 (начало созревания ягод), овощи 3–5 (созревание)</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>25 кг</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>100% растворимость · ЕС 0,1% р-ра 1,1 мСм/см · рН 1% р-ра 6</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница; Ячмень; Картофель; Овощи</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
         <is>
           <t>каталог производителя</t>
         </is>
@@ -2341,15 +4190,43 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Универсальное водорастворимое NPK-удобрение для сбалансированного питания в течение вегетации. Равновесное NPK для питания на всех стадиях: стимулирует рост и фотосинтез, снимает стресс от пестицидов, вредителей, засухи, переувлажнения и заморозков</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
           <t>202 ₽/кг</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr"/>
+      <c r="E71" s="2" t="inlineStr"/>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>N 18 · P2O5 18 · K2O 18 · MgO 1,4 · S 1,8 · B 0,03 · Cu 0,01 · Fe 0,15 · Mn 0,14 · Mo 0,003 · Zn 0,01 (%) · микро — хелат ЭДТА</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>Некорневая подкормка 2–5 кг/га. Фертигация: теплицы 0,05–0,2%, открытый грунт 0,1–0,2%</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>Зерновые 2–4 (кущение, выход в трубку), кукуруза 2–3 (5–6 листьев), подсолнечник 2–4 (8–10 листьев), рапс 2–5 (6–8 листьев), картофель 2–4 (формирование клубней), бобовые 2–4 (перед цветением)</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>25 кг</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>100% растворимость · ЕС 0,1% р-ра 0,9 мСм/см · рН 1% р-ра 5</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница; Ячмень; Рапс; Подсолнечник; Кукуруза; Картофель</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
         <is>
           <t>каталог производителя</t>
         </is>
@@ -2368,15 +4245,43 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Азотсодержащее водорастворимое удобрение для активного роста растений. Для декоративных, цветочных, ягодных и овощных культур и некорневых подкормок полевых: применимо при фертигации на всех типах орошения, совместимо с большинством пестицидов</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
           <t>196 ₽/кг</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr"/>
+      <c r="E72" s="2" t="inlineStr"/>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>N 19 · P2O5 6 · K2O 20 · MgO 3 · S 7 · B 0,03 · Cu 0,01 · Fe 0,1 · Mn 0,1 · Mo 0,003 · Zn 0,01 (%)</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>Некорневая подкормка 2–3 кг/га. Фертигация: теплицы 0,05–0,2%, открытый грунт 0,1–0,2%</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>Цветочно-декоративные, ягодные, овощные, зелень · полевые — зерновые и рапс 2–3 (начало созревания)</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>25 кг</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>100% растворимость · ЕС 0,1% р-ра 0,9 мСм/см · рН 1% р-ра 5</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница; Ячмень; Рапс; Овощи</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
         <is>
           <t>каталог производителя</t>
         </is>
@@ -2395,15 +4300,43 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Водорастворимое удобрение для цветения, плодоношения и налива урожая. Бесхлорное удобрение с повышенным калием и микроэлементами в хелатной форме для второй половины вегетации, корневых и некорневых подкормок; повышает устойчивость к стрессам</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
           <t>232 ₽/кг</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="D73" s="2" t="inlineStr"/>
+      <c r="E73" s="2" t="inlineStr"/>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>N 4 · P2O5 13 · K2O 36 · MgO 1,6 · S 7,7 · B 0,02 · Cu 0,01 · Fe 0,1 · Mn 0,1 · Mo 0,002 · Zn 0,01 (%)</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>Некорневая подкормка 2–5 кг/га. Фертигация: теплицы 0,05–0,2%, открытый грунт 0,1–0,2%</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>Масличные (бутонизация), зерновые (флаговый лист — колошение), сахарная свёкла (до смыкания рядков), картофель (рост клубней), бобовые (формирование бобов), овощи 3–5 (созревание)</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>25 кг</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>100% растворимость · ЕС 0,1% р-ра 1,1 мСм/см · рН 1% р-ра 6</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница; Ячмень; Картофель; Свёкла; Овощи</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
         <is>
           <t>каталог производителя</t>
         </is>
@@ -2422,15 +4355,43 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Водорастворимое фосфорное NPK-удобрение для стартовых стадий роста и развития корней. Повышенный фосфор на старте: стимулирует развитие корневой системы, активирует клеточное деление и обмен веществ; в бутонизацию и цветение ускоряет образование репродуктивных органов</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
           <t>227 ₽/кг</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="D74" s="2" t="inlineStr"/>
+      <c r="E74" s="2" t="inlineStr"/>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>N 12,9 · P2O5 40 · K2O 13,4 · MgO 0,1 · S 0,02 · B 0,015 · Cu 0,03 · Fe 0,08 · Mn 0,08 · Mo 0,003 · Zn 0,03 (%) · микро — хелат ЭДТА</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>Некорневая подкормка 2–4 кг/га. Фертигация: теплицы 0,05–0,2% (0,5–2 кг/1000 л), открытый грунт 0,1–0,2% (1–2 кг/1000 л)</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>Зерновые (начало кущения), кукуруза (3–5 листьев), подсолнечник (3–4 листа), рапс (3–4 листа), картофель 2–5 кг/га (клубнеобразование)</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>25 кг</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>100% растворимость · ЕС 0,1% р-ра 1,0 мСм/см · рН 1% р-ра 5</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница; Ячмень; Рапс; Подсолнечник; Кукуруза; Картофель</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
         <is>
           <t>каталог производителя</t>
         </is>
@@ -2449,15 +4410,43 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Осеннее фосфорно-калийное удобрение для подготовки растений к стрессам. Гранулированное удобрение под полевые культуры для основной обработки почвы осенью: повышенные фосфор и калий, нужные растениям в осенний период, прочные гранулы для равномерного внесения</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
           <t>106 ₽/кг</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="D75" s="2" t="inlineStr"/>
+      <c r="E75" s="2" t="inlineStr"/>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>N 5 · P2O5 21 · K2O 31 · Ca 0,55 · MgO 0,5 · S 0,7 · B 0,09 · Cu 0,08 · Fe 0,16 · Mn 0,16 · Mo 0,008 · Zn 0,09 (%)</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>Сахарная свёкла 300–600 кг/га · подсолнечник 200–300 · озимая пшеница 200–400 · кукуруза на зерно 400–600 кг/га</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>Полевые культуры — основное внесение осенью</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>МКР 800 кг / мешки 40 кг</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>Гранулы прочные, одного размера</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница; Ячмень; Рапс; Подсолнечник; Соя; Кукуруза; Горох; Гречиха; Лён; Свёкла; Картофель; Овощи</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
         <is>
           <t>каталог производителя</t>
         </is>
@@ -2476,15 +4465,43 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Комплексное водорастворимое NPK-удобрение с повышенным содержанием калия. Бесхлорное водорастворимое удобрение с хелатными микроэлементами для всех субстратов и типов полива, корневых и некорневых подкормок; повышает устойчивость к стрессам</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
           <t>207 ₽/кг</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="D76" s="2" t="inlineStr"/>
+      <c r="E76" s="2" t="inlineStr"/>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>N 12,3 · P2O5 11 · K2O 26 · MgO 2,5 · S 3,3 · B 0,02 · Cu 0,01 · Fe 0,1 · Mn 0,1 · Mo 0,002 · Zn 0,01 (%)</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>Некорневая подкормка 2–3 кг/га. Фертигация: теплицы 0,05–0,2%, открытый грунт 0,1–0,2%</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>Цветы, овощи, ягоды, зелень · зерновые и подсолнечник 2–3 (начало созревания)</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>25 кг</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>100% растворимость · ЕС 0,1% р-ра 1,0 мСм/см · рН 1% р-ра 5</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница; Ячмень; Подсолнечник; Овощи</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
         <is>
           <t>каталог производителя</t>
         </is>
@@ -2503,15 +4520,43 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Концентрированное водорастворимое NPK-удобрение для интенсивного питания. Полностью растворимое NPK с микроэлементами: подкормки в период корнеобразования и цветения, улучшает вкусовые свойства и устойчивость к болезням</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
           <t>203 ₽/кг</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="D77" s="2" t="inlineStr"/>
+      <c r="E77" s="2" t="inlineStr"/>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>N 16 · P2O5 20 · K2O 27 · B 0,02 · Cu 0,01 · Fe 0,1 · Mn 0,1 · Zn 0,01 (%)</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>Фертигация: теплицы 0,05–0,2%, открытый грунт 0,1–0,2% · корневые и некорневые подкормки</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>Цветы, ягоды, зелень — все субстраты, почвы и грунты, все типы полива</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>25 кг</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>100% растворимость</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>Овощи</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
         <is>
           <t>каталог производителя</t>
         </is>
@@ -2530,15 +4575,43 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Бесхлорное водорастворимое NPK-удобрение с магнием, серой и микроэлементами. Бесхлорное удобрение с повышенным калием и хелатными микроэлементами для фертигации: защищённый грунт, гидропоника, инертные и органические субстраты, ягоды, овощи и сады</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
           <t>225 ₽/кг</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="D78" s="2" t="inlineStr"/>
+      <c r="E78" s="2" t="inlineStr"/>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>N 6,4 · P2O5 11 · K2O 31 · MgO 2,6 · S 4,4 · B 0,02 · Cu 0,01 · Fe 0,1 · Mn 0,1 · Mo 0,002 · Zn 0,01 (%)</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>Фертигация и гидропоника: теплицы 0,05–0,2%, открытый грунт 0,1–0,2%</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>Огурец, томат, цветы, ягоды — защищённый и открытый грунт, все типы полива</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>25 кг</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>100% растворимость · ЕС 0,1% р-ра 1,0 мСм/см · рН 1% р-ра 6</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>Овощи</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
         <is>
           <t>каталог производителя</t>
         </is>
@@ -2557,15 +4630,43 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Концентрированное бесхлорное калийное удобрение с серой. Калий без хлора: снижает нагрузку на чувствительные к хлору и молодые растения, увеличивает размер и плотность плодов, содержание сахара и пигментов, устойчивость к засухе и к хранению</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
           <t>103 ₽/кг</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="D79" s="2" t="inlineStr"/>
+      <c r="E79" s="2" t="inlineStr"/>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>K2O 50 · S 17 (%)</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>Томаты, огурцы, цветочные 15–20 г/м² · картофель, капуста, свёкла, морковь 25–30 г/м² · редис, лук, салат 5–10 г/м² · защищённый грунт 30–40 г/м² · плодовые деревья 150–200 г/растение</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>Плодовые, ягодные, овощные, чувствительные к хлору культуры</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>МКР 1000 кг / мешки 35 кг</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>Бесхлорное</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>Овощи</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
         <is>
           <t>каталог производителя</t>
         </is>
@@ -2584,15 +4685,43 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Гранулированное бесхлорное удобрение для овощных и плодово-ягодных культур. Гранулированное удобрение для овощных и плодово-ягодных: микроэлементы ускоряют развитие, снижают риск грибных и бактериальных болезней, калий улучшает лёжкость</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
           <t>112 ₽/кг</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="D80" s="2" t="inlineStr"/>
+      <c r="E80" s="2" t="inlineStr"/>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>N 12 · P2O5 8 · K2O 14 · Ca 0,6 · MgO 2 · SO3 8 · B 0,09 · Cu 0,08 · Fe 0,16 · Mn 0,16 · Mo 0,08 · Zn 0,09 (%)</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>Картофель 600–800 кг/га · овощные 600–1000 кг/га · ягодные 200–400 кг/га · декоративные 600–800 кг/га</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>Картофель, овощные, ягодные, декоративные культуры</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>МКР 800 кг / мешки 40 кг</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>Гранулы, не пылят</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>Картофель; Овощи</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
         <is>
           <t>каталог производителя</t>
         </is>
@@ -2611,15 +4740,39 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Пролонгированное удобрение для хвойных и кислолюбивых растений. Гранулированное удобрение пролонгированного действия без хлора для хвойных, рододендронов, гортензий и голубики: понижает pH почвы до нужного уровня, даёт насыщенный цвет хвои</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
           <t>по запросу</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="D81" s="2" t="inlineStr"/>
+      <c r="E81" s="2" t="inlineStr"/>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>N 9,9 · P2O5 7 · K2O 14 · MgO 6,9 · SO3 40,8 · B 0,05 · Cu 0,03 · Mn 0,1 · Zn 0,06 (%)</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>При посадке и подкормке 30–40 г на растение · поверхностно 60 г/м², 1–2 раза за вегетацию</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>Хвойные, рододендроны, азалии, гортензии, голубика, садовая черника</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>800 кг, 40 кг</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>Пролонгированное действие, понижает рН почвы, без хлора</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
         <is>
           <t>каталог производителя</t>
         </is>
@@ -2638,15 +4791,43 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Бесхлорное калийное удобрение растительного происхождения с серой и магнием. Бесхлорный калий растительного происхождения из лузги подсолнечника с повышенным магнием и серой: для почв, бедных магнием, и культур, чувствительных к хлору</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
           <t>48 ₽/кг</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="D82" s="2" t="inlineStr"/>
+      <c r="E82" s="2" t="inlineStr"/>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>K2O 37 · P2O5 4,1 · SO3 10 · MgO 7,1 · CaO 7,1 · Fe 0,1 · Mn 0,01 · Zn 0,02 · Cu 0,02 (%)</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>Яровые зерновые, кукуруза, рапс, подсолнечник, озимая пшеница 200–400 кг/га · картофель и корнеплоды 300–350 · томат, огурец, плодово-ягодные 200–250 кг/га</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>Зерновые, кукуруза, рапс, подсолнечник, картофель, корнеплоды, плодово-ягодные</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>МКР 800 кг / мешки 25 кг</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>Бесхлорное, растительного происхождения (лузга подсолнечника)</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница; Ячмень; Рапс; Подсолнечник; Кукуруза; Картофель</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
         <is>
           <t>каталог производителя</t>
         </is>
@@ -2665,15 +4846,39 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Азотно-серно-магниевое удобрение для листовых подкормок. Источник азотного питания с выверенным соотношением азота, серы и магния: оптимизирует азотный обмен, усиливает усвоение других макро- и микроэлементов, снижает риск хлороза</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
           <t>по запросу</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="D83" s="2" t="inlineStr"/>
+      <c r="E83" s="2" t="inlineStr"/>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>Азот общий 250–280 г/л · сера (SO3) 40–50 г/л · магний (MgO) 7–10 г/л · плотность 1,2–1,3 г/см³, рН 5,5–7,5</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>Листовая подкормка</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>Все декоративные и сельскохозяйственные культуры</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>Плотность 1,2–1,3 г/см³, рН 5,5–7,5</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница; Ячмень; Рапс; Подсолнечник; Соя; Кукуруза; Горох; Гречиха; Лён; Свёкла; Картофель; Овощи</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
         <is>
           <t>каталог производителя</t>
         </is>
@@ -2692,15 +4897,39 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Фосфорно-калийное удобрение для налива и качества урожая. Насыщенный усваиваемыми фосфат-ионами раствор: оптимизирует обменные процессы, устраняет дисбаланс по макроэлементам, способствует накоплению сахаров и сухих веществ, улучшает лёжкость урожая</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
           <t>по запросу</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="D84" s="2" t="inlineStr"/>
+      <c r="E84" s="2" t="inlineStr"/>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Азот общий 65–90 г/л · фосфор (P2O5) 410–450 г/л · калий (K2O) 140–150 г/л · плотность 1,35–1,45 г/см³, рН 6,5–7,5</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>Листовая подкормка</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>Все культуры · особенно масличные — подсолнечник, рапс, соя</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>Плотность 1,35–1,45 г/см³, рН 6,5–7,5</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница; Ячмень; Рапс; Подсолнечник; Соя; Кукуруза; Горох; Гречиха; Лён; Свёкла; Картофель; Овощи</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
         <is>
           <t>каталог производителя</t>
         </is>
@@ -2719,15 +4948,43 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
+          <t>по запросу</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
           <t>Мучнистая роса, ржавчина (бурая, жёлтая, стеблевая), септориоз, пиренофороз, фузариоз (частично), церкоспороз, фомоз, альтернариоз</t>
         </is>
       </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>по запросу</t>
-        </is>
-      </c>
       <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>пропиконазол 250 г/л + ципроконазол 80 г/л</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr"/>
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>0,4–0,75 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница яровая/озимая, свёкла сахарная</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>5 л × 4</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница; Свёкла</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
         <is>
           <t>прайс «Сатурн» 2026</t>
         </is>
@@ -2746,15 +5003,43 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Ржавчина бурая, стеблевая, жёлтая; мучнистая роса, септориоз листьев и колоса, пиренофороз, карликовая ржавчина, ринхоспориоз, сетчатая и тёмно-бурая пятнистости, церкоспороз, фомоз, оидиум, альтернариоз, аскохитоз, антракноз</t>
+          <t>1562,5 ₽/л</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>1562,5 ₽/л</t>
+          <t>Ржавчина бурая, стеблевая, жёлтая · мучнистая роса, септориоз листьев и колоса, пиренофороз, карликовая ржавчина, ринхоспориоз, сетчатая и тёмно-бурая пятнистости, церкоспороз, фомоз, оидиум, альтерна</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>пропиконазол 300 г/л + тебуконазол 200 г/л</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr"/>
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>0,2–0,6 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница яровая/озимая, ячмень яровой/озимый, свёкла сахарная, виноград, рапс яровой/озимый, соя</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>10 л × 2</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница; Ячмень; Рапс; Соя; Свёкла</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
         <is>
           <t>прайс «Сатурн» 2026</t>
         </is>
@@ -2773,15 +5058,43 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Ржавчина бурая, стеблевая, жёлтая, корончатая; мучнистая роса, септориоз листьев и колоса, пиренофороз, карликовая ржавчина, сетчатая, тёмно-бурая и красно-бурая пятнистости, ринхоспориоз, альтернариоз, склеротиниоз</t>
+          <t>1417,5 ₽/л</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>1417,5 ₽/л</t>
+          <t>Ржавчина бурая, стеблевая, жёлтая, корончатая · мучнистая роса, септориоз листьев и колоса, пиренофороз, карликовая ржавчина, сетчатая, тёмно-бурая и красно-бурая пятнистости, ринхоспориоз, альтернари</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>тебуконазол 250 г/л</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr"/>
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>0,75–1 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница яровая/озимая, ячмень яровой/озимый, рожь озимая, овёс, рапс яровой/озимый</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>10 л × 2</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница; Ячмень; Рапс</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
         <is>
           <t>прайс «Сатурн» 2026</t>
         </is>
@@ -2800,17 +5113,4870 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Волски Биохим · листовые подкормки</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
           <t>900 ₽</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>нет в прайсе 13.10 — позиция только на сайте</t>
+      <c r="D88" s="2" t="inlineStr"/>
+      <c r="E88" s="2" t="inlineStr"/>
+      <c r="F88" s="2" t="inlineStr"/>
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>0,5 л/га</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>раствор</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>Все</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>нет в прайсе 13.10 — только на сайте</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M88"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Товар</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Категория</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Цена</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Спектр действия</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Действующее вещество</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Состав</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Действие</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Норма расхода</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Культуры и фазы</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Фасовка</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Физико-химические показатели</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Культура</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Источник описания</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Биостик Терра</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Адъюванты и спецпрепараты</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>635 ₽/л</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Олигополисахарид бактериального происхождения, гетероферментивные молочнокислые бактерии и комплекс дополнительных веществ</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Предотвращает растрескивание плодов и осыпание зерна</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>1 л/га на 100–200 л воды/га</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>прайс «Сатурн» 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Вега 90, Ж</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Адъюванты и спецпрепараты</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>220 ₽/л</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Этоксилат изодецилового спирта</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>ПАВ-адъювант: снижает поверхностное натяжение раствора, капля растекается и дольше держится на листе, пестицид проникает лучше · расход пестицидов меньше на 10–15%</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>0,2–0,5</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>офсайт: npk-x.ru · прайс «Сатурн» 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Вега АнтиПена, КЭ</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Адъюванты и спецпрепараты</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>по запросу</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Силиконовая эмульсия, стабилизирующие добавки и ПАВ</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Кремнийорганические соединения быстро разрушают структуру пены и не дают ей образоваться снова, уменьшают контакт жидкой и газовой фаз, обеспечивают равномерную циркуляцию смеси</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,01–0,05</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>офсайт: npk-x.ru · прайс «Сатурн» 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Вега Баланс, ВР</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Адъюванты и спецпрепараты</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>по запросу</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Комплекс органических и минеральных кислот, органических комплексонов и кремнийорганические соединения</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Органические кислоты снижают pH и жёсткость воды, антивспенивающие компоненты образуют плёнку на границе жидкости и воздуха и мешают образованию пузырьков · рабочий pH смеси 5,0–6,0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,1–1</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>офсайт: npk-x.ru · прайс «Сатурн» 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Вега Голд, Ж</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Адъюванты и спецпрепараты</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1350 ₽/л</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Гептаметилтрисилоксан, модифицированный полиалкиленоксидом, 100%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Смачиватель и пенетрант на гептаметилтрисилоксане: снижает натяжение раствора и усиливает проникновение пестицидов, позволяет сократить расход воды на 30–50%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,01–0,1</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>офсайт: npk-x.ru · прайс «Сатурн» 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Вега Клей</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Адъюванты и спецпрепараты</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>по запросу</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Кедровая смола, масло крабе, канифоль, адъюванты</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Клей для крестоцветных и зернобобовых — против опадения и потери зерна</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,8–1,5</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>прайс «Сатурн» 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Вега Турбо</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Адъюванты и спецпрепараты</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>426 ₽/л</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Комплексоны 20%, ПАВ 5%, подготовленная вода</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Моющее средство для опрыскивателя: комплексоны и ПАВ переводят солевой налёт в раствор и снимают остатки пестицидов с баков, трубопроводов, фильтров и форсунок</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,1–0,3</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>офсайт: npk-x.ru · прайс «Сатурн» 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Вега Эмульс, КЭ</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Адъюванты и спецпрепараты</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>по запросу</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Рапсовое масло около 85% и эмульгаторы около 15%</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Рапсовое масло с эмульгаторами: раствор растекается по листу, масляная основа удерживает препарат, замедляет испарение и помогает пройти через кутикулу, стабилизирует баковые смеси</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,5–1</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>офсайт: npk-x.ru · прайс «Сатурн» 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Волски Оптим</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Адъюванты и спецпрепараты</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>700 ₽/л</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Органические кислоты, хелатообразователь, н-ПАВ, пеногаситель, индикатор</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Понижает pH рабочего раствора, предотвращает щелочной гидролиз пестицидов, связывает соли жёсткости — кальций, магний, железо, снижает поверхностное натяжение и пенообразование</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>30–150 мл на 100 л</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>офсайт: volskybiochem.com · прайс «Сатурн» 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Альфард, ВР</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Гербициды</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1040 ₽/л</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Однолетние и некоторые многолетние двудольные сорняки</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>фомесафен 250 г/л</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1,5–2 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Соя</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>20 л, штабель</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>Соя</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>прайс «Сатурн» 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Ампир Экстра, ВР</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Гербициды</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>540 ₽/л</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Гербицид сплошного действия</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>глифосат (калийная соль) 540 г/л</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1,4–5 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Пары, поля под посев, земли не с/х</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>20 л, штабель</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница;Ячмень;Рапс;Подсолнечник;Соя;Кукуруза;Горох;Гречиха;Лён;Свёкла;Картофель;Овощи</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>прайс «Сатурн» 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Ампир, ВР</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Гербициды</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>по запросу</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Гербицид сплошного действия</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>глифосат (изопропиламинная соль) 360 г/л</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2–8 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Поля, пары под посев</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>20 л, штабель</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница;Ячмень;Рапс;Подсолнечник;Соя;Кукуруза;Горох;Гречиха;Лён;Свёкла;Картофель;Овощи</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>прайс «Сатурн» 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Гекстар, ВДГ</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Гербициды</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2590 ₽/кг</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Однолетние двудольные сорняки, в т.ч. устойчивые к 2,4-Д и МЦПА</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>трибенурон-метил 750 г/кг</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,01–0,05 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница яровая/озимая, ячмень яровой/озимый, овёс, SU-подсолнечник</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0,5 кг × 10</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница;Ячмень;Подсолнечник</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>прайс «Сатурн» 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Зазофен, ВР</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Гербициды</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>1825 ₽/л</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Однолетние двудольные и некоторые однолетние злаковые сорняки</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>бентазон 360 г/л + ацифлуорфен 80 г/л</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>1–1,5 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Соя</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>5 л × 4</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>Соя</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>прайс «Сатурн» 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Злакофф, КЭ</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Гербициды</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>877,5 ₽/л</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Однолетние злаковые, многолетние злаковые (пырей ползучий)</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>клетодим 240 г/л</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,2–1 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Свёкла сахарная, рапс яровой/озимый, соя, лён, подсолнечник</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>5 л × 4</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>Рапс;Подсолнечник;Соя;Свёкла;Лён</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>прайс «Сатурн» 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Кирасир, СЭ</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Гербициды</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>540 ₽/л</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Однолетние двудольные, в т.ч. устойчивые к 2,4-Д и МЦПА, и некоторые многолетние двудольные</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2,4-Д кислоты (2-этилгексиловый эфир) 410 г/л + флорасулам 7,4 г/л</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,3–0,5 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница яровая/озимая, ячмень яровой, кукуруза, просо, сорго</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>10 л × 2</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница;Ячмень;Кукуруза</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>прайс «Сатурн» 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Клео, ВДГ</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Гербициды</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>4050 ₽/кг</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Однолетние и некоторые многолетние двудольные, в т.ч. сложноцветные</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>клопиралид 750 г/кг</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,12 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Свёкла сахарная, рапс яровой (семена), лён долгунец/масличный</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>1 кг × 10</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>Рапс;Свёкла;Лён</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>прайс «Сатурн» 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Клордин, КЭ</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Гербициды</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>1065 ₽/л</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Однолетние двудольные и злаковые сорняки</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>кломазон 480 г/л</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,7–1 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Соя</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>5 л × 4</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>Соя</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>прайс «Сатурн» 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Курсар, ВР</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Гербициды</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>880 ₽/л</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Однолетние злаковые и двудольные сорняки</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>имазамокс 40 г/л</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,75–1 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Соя, горох и нут (на зерно)</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>5 л × 4</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>Соя;Горох</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>прайс «Сатурн» 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Метолс, КЭ</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Гербициды</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>1150 ₽/л</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Однолетние злаковые и некоторые двудольные сорняки</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>С-метолахлор 960 г/л</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>1,3–1,6 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Кукуруза, соя, подсолнечник, рапс яровой, свёкла сахарная</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>5 л × 4</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>Рапс;Подсолнечник;Соя;Кукуруза;Свёкла</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>прайс «Сатурн» 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Поллукс, ЭМВ</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Гербициды</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>745 ₽/л</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Однолетние злаковые сорняки</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>феноксапроп-П-этил 69 г/л + антидот клоквинтосет-мексил 34,5 г/л</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,8–1 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница яровая/озимая, ячмень яровой</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>10 л × 2</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница;Ячмень</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>прайс «Сатурн» 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Ранголи-Базорон, ВР</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Гербициды</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>1040 ₽/л</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Однолетние двудольные сорняки</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>бентазон 480 г/л</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>1,5–4 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница яровая/озимая, ячмень яровой/озимый, рожь яровая/озимая, овёс, горох, нут, соя, лён-долгунец</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>20 л, штабель</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница;Ячмень;Соя;Горох;Лён</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>прайс «Сатурн» 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Спика, КЭ</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Гербициды</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>850 ₽/л</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Однолетние злаковые, многолетние злаковые (пырей ползучий)</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>галоксифоп-П-метил 108 г/л</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0,5–1 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Рапс яровой/озимый, соя, подсолнечник</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>5 л × 4 · 10 л × 2</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>Рапс;Подсолнечник;Соя</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>прайс «Сатурн» 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Тифилагро, ВДГ</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Гербициды</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>5625 ₽/кг</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Однолетние и некоторые многолетние двудольные, в т.ч. устойчивые к 2,4-Д и МЦПА</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>тифенсульфурон-метил 750 г/л</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,006–0,025 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница яровая/озимая, ячмень яровой/озимый, кукуруза (на зерно), соя, лён долгунец/масличный</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>0,1 кг × 100</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница;Ячмень;Соя;Кукуруза;Лён</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>прайс «Сатурн» 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Торпеда, ВДГ</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Гербициды</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>по запросу</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Однолетние и некоторые многолетние двудольные сорняки</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>тифенсульфурон-метил 500 г/кг + флорасулам 170 г/кг</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,025–0,035 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Зерновые колосовые яровые/озимые за исключением овса, кукуруза (зерно)</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>0,5 кг</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница;Ячмень;Кукуруза</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>прайс «Сатурн» 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Укротитель, КЭ</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Гербициды</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>800 ₽/л</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Однолетние злаковые (овсюг, метлица обыкновенная, щетинники, мятлик, просовидные)</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>феноксапроп-П-этил 100 г/л + антидот клоквинтосет-мексил 27 г/л</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>0,4–0,9 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница яровая/озимая</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>5 л × 4 · 10 л × 2</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>прайс «Сатурн» 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Царумин, ВК</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Гербициды</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>880 ₽/л</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Однолетние двудольные сорные растения</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>МЦПА (диметиламинная + натриевая + калиевая соль) 500 г/л</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,5–1,5 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница яровая/озимая, ячмень яровой/озимый, рожь озимая, овёс, горох (на зерно), картофель, лён-долгунец</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>10 л × 2</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница;Ячмень;Картофель;Горох;Лён</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>прайс «Сатурн» 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Челленджер, ВРК</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Гербициды</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>945 ₽/л</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Однолетние злаковые и двудольные и некоторые многолетние сорняки</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>имазамокс 33 г/л + имазапир 15 г/л</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>1–1,2 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Подсолнечник (на масло и зерно), устойчивый к имидазолинонам</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>5 л × 4 · 10 л × 2</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>Подсолнечник</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>прайс «Сатурн» 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Ранголи-Реголон, ВР</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Десиканты</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>392 ₽/л</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Десикация</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>дикват дибромид 150 г/л (пересчёт на дикват-ион 80,3 г/л)</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>2 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Подсолнечник</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>10 л × 2</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>Подсолнечник</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>прайс «Сатурн» 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Ригель Форте, ВР</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Десиканты</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>540 ₽/л</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Десикация</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>дикват дибромид 240 г/л (пересчёт на дикват-ион 128 г/л)</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>0,7–1,8 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Подсолнечник, соя, рапс яровой, горох, картофель</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>10 л × 2</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>Рапс;Подсолнечник;Соя;Картофель;Горох</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>прайс «Сатурн» 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Альфацин, КЭ</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Инсектициды</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>510 ₽/л</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Клоп вредная черепашка, блошки, тли, цикадки, трипсы, пьявица, рапсовый цветоед, крестоцветные блошки, свекловичная листовая тля и минирующая муха, гороховая зерновка и плодожорка, долгоносики, саранчовые</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>альфа-циперметрин 100 г/л</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>0,1–0,3 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница яровая/озимая, ячмень яровой/озимый, рапс яровой/озимый, картофель, свёкла кормовая и сахарная, горох, люцерна, участки, заселённые саранчовыми</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>5 л × 4 · 10 л × 2</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница;Ячмень;Рапс;Картофель;Свёкла;Горох</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>прайс «Сатурн» 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Гарпун, КС</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Инсектициды</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>1150 ₽/л</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Клоп вредная черепашка, хлебные жуки и блошки, пшеничные трипсы, тли, внутристеблевые мухи, пьявица, стеблевые пилильщики, свекловичные долгоносики, луговой мотылёк, гороховая зерновка и плодожорка, бобовая огнёвка, соевая плодожорка, клубеньковый долгоносик, рапсовый цветоед и пилильщик</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>ацетамиприд 115 г/л + лямбда-цигалотрин 106 г/л</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>0,1–0,5 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница яровая/озимая, ячмень яровой, свёкла сахарная, горох, нут, соя, рапс яровой</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>5 л × 4</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница;Ячмень;Рапс;Соя;Свёкла;Горох</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>прайс «Сатурн» 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Кастра, КС</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Инсектициды</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>1125 ₽/л</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Клубеньковый долгоносик, многоягодные совки, бобовая огнёвка, крестоцветные блошки, рапсовый пилильщик и цветоед, рапсовый семенной скрытнохоботник, клоп вредная черепашка, тли, хлебные жуки, пшеничный трипс, хлебные блошки, пьявицы</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>клотианидин 140 г/л + лямбда-цигалотрин 100 г/л</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>0,1–0,25 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Зерновые колосовые (кроме овса), рапс яровой/озимый, соя</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>5 л × 4</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница;Ячмень;Рапс;Соя</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>прайс «Сатурн» 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Ранголи Норил, КЭ</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Инсектициды</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>1040 ₽/л</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Хлебная жужелица, клоп вредная черепашка, хлебные жуки, злаковые тли, пьявицы, крестоцветные блошки</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>клотианидин 140 г/л + лямбда-цигалотрин 100 г/л</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>0,5–1 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница яровая/озимая, ячмень, рапс</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>5 л × 4 · 10 л × 2</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница;Ячмень;Рапс</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>прайс «Сатурн» 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Волски Моно-Бор</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Листовые подкормки</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>760 ₽/л</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr"/>
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Бор 131 г/л (13,1%) · N 60 г/л (6%) · органический проникатель</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Бор в органической форме с мембранным проникателем: деление клеток и построение клеточных стенок, рост пыльцевых трубок и оплодотворение завязи, отток продуктов фотосинтеза в клубни и корнеплоды</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>0,5 л/га, 1–2 обработки (до 1 л/га при низком содержании бора). Рабочий раствор 100–300 л/га</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Подсолнечник (формирование корзинки), сах. свёкла (перед смыканием рядков), картофель (смыкание рядков), горох/соя/рапс/горчица (бутонизация, перед цветением)</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>канистра 10 л</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>Плотность 1,3 г/см³</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>Рапс;Подсолнечник;Соя;Картофель;Свёкла;Горох</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>офсайт: volskybiochem.com · каталог производителя</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Волски Моно-Железо</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Листовые подкормки</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>430 ₽/л</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr"/>
+      <c r="E37" s="2" t="inlineStr"/>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Железо 100 г/л (10%) · N 41 г/л (4,1%) · органический мембранный проникатель</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Железо в хелате ОЭДФ: образование хлорофилла и усиление фотосинтеза, белковый обмен и синтез ауксинов, устранение хлороза от нехватки железа</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Овощные и плодово-ягодные 0,5–1,0 л/га (1–3 обработки), зерновые 0,5 л/га (1 обработка). Рабочий раствор 100–300 л/га</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Овощные, зерновые, плодово-ягодные — при хлорозе и недостатке железа</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>канистра 10 л</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>Плотность 1,3 г/см³</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница;Ячмень;Овощи</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>офсайт: volskybiochem.com · каталог производителя</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Волски Моно-Медь</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Листовые подкормки</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>465 ₽/л</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Медь 82 г/л (8,2%) · N 41 г/л (4,1%) · органический мембранный проникатель</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Медь в хелате ОЭДФ участвует в синтезе окислительно-восстановительных ферментов, усиливает фотосинтез и дыхание, повышает устойчивость злаковых к полеганию и грибным болезням</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>0,5–1,0 л/га. Рабочий раствор 100–300 л/га</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Культуры при недостатке меди</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>канистра 10 л</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>Плотность 1,2 г/см³</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница;Ячмень;Рапс;Подсолнечник;Соя;Кукуруза;Горох;Гречиха;Лён;Свёкла;Картофель;Овощи</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>офсайт: volskybiochem.com · каталог производителя</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Волски Моно-Сера</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Листовые подкормки</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>490 ₽/л</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr"/>
+      <c r="E39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Сера 72% · N 27 г/л (2,7%) · Mg 31 г/л (3,1%)</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Сера входит в состав белков и ферментов, улучшает усвоение азота из почвы · магний усиливает углеводный и липидный обмен. Повышает белок и клейковину у зерновых, масличность у рапса и горчицы</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>0,5–1,0 л/га (до 1 л/га при низком содержании серы). Рабочий раствор 100–300 л/га</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Рапс, сурепица, рыжик (3–7 лист — розетка) · горох, соя, нут (3–4 лист — стеблевание) · зерновые (колошение — флаговый лист)</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>канистра 10 л</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>Плотность 1,4 г/см³</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница;Ячмень;Рапс;Соя;Горох</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>офсайт: volskybiochem.com · каталог производителя</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Волски Моно-Цинк</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Листовые подкормки</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>728 ₽/л</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr"/>
+      <c r="E40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Цинк 75 г/л (7,5%) · N 41 г/л (4,1%) · влагоудерживающий компонент</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Цинк в хелате ЭДТА улучшает усвоение фосфора, активирует ферменты, регулирует корнеобразование и накопление фитогормонов · влагоудерживающая добавка повышает засухоустойчивость</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>0,5 л/га, 1 обработка (до 1 л/га при низком содержании цинка). Рабочий раствор 100–300 л/га</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Кукуруза (5–9 лист) · другие культуры — рост листьев и стеблей</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>канистра 10 л</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>Плотность 1,2 г/см³</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>Кукуруза</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>офсайт: volskybiochem.com · каталог производителя</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Диформа Бор-Молибден</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Листовые подкормки</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>1290 ₽/л</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr"/>
+      <c r="E41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Бор 100 г/л (10%) · Молибден 40 г/л (4%) · N 70 г/л (7%) · мембранный проникатель. Самое высокое содержание молибдена в линейке</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Бор и молибден в органической форме с мембранным проникателем: молибден улучшает усвоение азота и работу клубеньковых бактерий, бор улучшает опыление и оплодотворение цветков</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Семена 0,5–1,0 л/т · листовая подкормка 0,5–1,5 л/га</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Зернобобовые — горох, соя, нут, чечевица · семенники многолетних трав, лён</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>Плотность 1,4 г/см³</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>Соя;Горох;Лён</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>офсайт: volskybiochem.com · каталог производителя</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Диформа Кальций-Азот</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Листовые подкормки</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>650 ₽/л</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr"/>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Кальций 100 г/л (10%) · Азот 50 г/л (5%)</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Кальций в хелате ЭДТА укрепляет кутикулу и клеточные стенки, поддерживает кислотно-щелочное равновесие и синтез хлорофилла, снижает вершинную гниль и растрескивание плодов, повышает лёжкость</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>0,5–2,0 л/га, листовая подкормка</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Плодово-ягодные, овощи, картофель</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>Плотность 1,2 г/см³</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>Картофель;Овощи</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>офсайт: volskybiochem.com · каталог производителя</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Диформа Кобальт-Селен</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Листовые подкормки</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>1020 ₽/л</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr"/>
+      <c r="E43" s="2" t="inlineStr"/>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Кобальт 50 г/л (5%) · Селен 1 г/л (0,1%) · Азот 10 г/л (1%) · Сера 70 г/л (7%) · Фосфор 13 г/л (1,3%)</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Кобальт в хелате ОЭДФ и селен: антиоксидантное действие, связывание токсичных веществ, устойчивость клеточных мембран, лучшее усвоение макро- и микроэлементов, обогащение кормов</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>0,5–1,0 л/га, листовая подкормка</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>Многолетние травы (клевер, люцерна, козлятник и смеси со злаковыми), кормовые культуры</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>Плотность 1,1 г/см³</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>офсайт: volskybiochem.com · каталог производителя</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Диформа Кремний-Калий</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Листовые подкормки</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>695 ₽/л</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Кремний 340 г/л (34%) · Калий 160 г/л (16%) · Азот 2,3 г/л (0,23%), амидная форма</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Кремний с калием укрепляют клеточные стенки, ускоряют синтез антиоксидантных ферментов, снижают транспирацию при засухе и токсичность избытка железа и алюминия</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Семена 0,2–0,5 л/т · листовая подкормка 0,2–1,0 л/га</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Зерновые, плодово-ягодные, овощи</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>Плотность 1,3 г/см³</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница;Ячмень;Овощи</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>офсайт: volskybiochem.com · каталог производителя</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Диформа Магний-Марганец</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Листовые подкормки</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>520 ₽/л</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr"/>
+      <c r="E45" s="2" t="inlineStr"/>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Магний 50 г/л (5%) · Марганец 10 г/л (1%) · Азот 10 г/л (1%) · Сера 110 г/л (11%) · Фосфор 36 г/л (3,6%)</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Магний и марганец в хелате ОЭДФ усиливают фотосинтез и накопление сухого вещества, устраняют хлорозы · влагоудерживающая добавка снижает испарение раствора и повышает засухоустойчивость</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>0,5–2,0 л/га, листовая подкормка</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Плодово-ягодные, сахарная свёкла, кукуруза</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>Плотность 1,2 г/см³</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>Кукуруза;Свёкла</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>офсайт: volskybiochem.com · каталог производителя</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Диформа Магний-Цинк</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Листовые подкормки</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>653 ₽/л</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr"/>
+      <c r="E46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Магний 75 г/л (7,5%) · Цинк 30 г/л (3%) · Азот 52 г/л (5,2%) · Сера 37 г/л (3,7%) · Фосфор 14 г/л (1,4%) · хелат ОЭДФ. Самое высокое содержание магния</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Магний в хелате ОЭДФ усиливает синтез хлорофилла и ауксинов, стабилизирует дыхание и обмен углеводов, повышает устойчивость к жаре, засухе и морозу · с цинком действуют синергично</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>0,5–2,0 л/га, листовая подкормка</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Кукуруза, сахарная свёкла, картофель, овощи, плодово-ягодные</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>Плотность 1,2 г/см³</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>Кукуруза;Картофель;Свёкла;Овощи</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>офсайт: volskybiochem.com · каталог производителя</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Диформа Марганец-Бор</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Листовые подкормки</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>1290 ₽</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr"/>
+      <c r="E47" s="2" t="inlineStr"/>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Марганец 50 г/л (5%) · Бор 25 г/л (2,5%) · Азот 25 г/л (2,5%)</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Марганец в хелате ОЭДФ с мембранным проникателем усиливает окислительно-восстановительные реакции и отток пластических веществ, стимулирует синтез предшественников фитогормонов</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>0,5–2,0 л/га, листовая подкормка</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Плодово-ягодные, овощи, картофель, сахарная свёкла, подсолнечник</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>Плотность 1,2 г/см³</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>Подсолнечник;Картофель;Свёкла;Овощи</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>офсайт: volskybiochem.com · каталог производителя</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Диформа Марганец-Цинк</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Листовые подкормки</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>605 ₽/л</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr"/>
+      <c r="E48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Марганец 56 г/л (5,6%) · Цинк 28 г/л (2,8%) · Азот 10 г/л (1%) · Сера 120 г/л (12%) · Фосфор 6 г/л (0,6%) · хелат ОЭДФ</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Марганец и цинк в хелате ОЭДФ усиливают окислительно-восстановительные реакции и синтез фитогормонов · влагоудерживающая добавка повышает засухо- и жароустойчивость</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>0,5–2,0 л/га, листовая подкормка</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Плодово-ягодные, овощи, картофель, кукуруза, сахарная свёкла</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>Плотность 1,2 г/см³</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>Кукуруза;Картофель;Свёкла;Овощи</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>офсайт: volskybiochem.com · каталог производителя</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Микроэл Пивоваренный ячмень</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Листовые подкормки</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>651 ₽</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr"/>
+      <c r="E49" s="2" t="inlineStr"/>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Азотфиксирующий и фотосинтезирующий комплекс микроэлементов линейки «Микроэл», вариант для пивоваренного ячменя</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Ограничивает азотфиксацию, препятствует избыточному накоплению белка, стимулирует фотосинтез и накопление углеводов</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>0,2–0,4 л/га, 2 обработки. Рабочий раствор 30–300 л/га</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Пивоваренный ячмень</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>канистра 10 л</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>Плотность 1,3 г/см³</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>Ячмень</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>офсайт: volskybiochem.com · каталог производителя</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Микроэл Универсальный</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Листовые подкормки</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>651 ₽/л</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr"/>
+      <c r="E50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Mn 3,4 · Mo 2,2 · MgO 15 · Zn 14 · Cu 6 · Fe 3,0 · Co 0,8 · B 1,6 · SO3 68 · N 4 · K2O 0,3 г/л · + Cr, Ni, Li, Se. 15 элементов, микро — хелат ЭДТА</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>4 макро- и 11 микроэлементов в хелатной форме: стимулирует фотосинтез и азотфиксацию, помогает переносить стресс от гербицидов, засухи и заморозков, повышает клейковину пшеницы</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>0,2–0,5 л/га, 2 обработки (при однократной — до 0,4 л/га). Рабочий раствор 30–300 л/га</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Кукуруза 0,2 (5–9 лист, трубкование), подсолнечник 0,2, сах. свёкла 0,4, зернобобовые 0,2, озимые и яровые зерновые 0,2 (кущение, колошение), картофель 0,4, плодово-ягодные 0,5–1,0</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>Плотность 1,3 г/см³</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница;Ячмень;Подсолнечник;Кукуруза;Картофель;Свёкла</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>офсайт: volskybiochem.com · каталог производителя</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Реликт М Бор</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Листовые подкормки</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>765 ₽/л</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr"/>
+      <c r="E51" s="2" t="inlineStr"/>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Бор (B) 130–150 г/л (в соединении с этаноламином ≥460 г/л) · азот (N) 90–110 г/л · молибден (MoO3) 4–8 г/л · рН 8–9,5</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Бор в органической форме: рост пыльцевых трубок и завязываемость плодов, углеводный и белковый обмен, регуляция ауксинов, лёжкость корнеплодов, баланс питания кальцием</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>0,5–1,5 л/га листовая подкормка</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Все сельхозкультуры. Подсолнечник (2–5 пар листьев, начало образования корзинки), сахарная свёкла 1,0–1,5 л/га</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>раствор</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>рН 8–9,5</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница;Ячмень;Рапс;Подсолнечник;Соя;Кукуруза;Горох;Гречиха;Лён;Свёкла;Картофель;Овощи</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>офсайт: relict-dv.ru · каталог производителя</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Реликт М Кремний</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Листовые подкормки</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>470 ₽/л</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr"/>
+      <c r="E52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Кремний (SiO2) 210–230 г/л · Калий (K2O) 90–110 г/л · рН 11–12</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Кремний с калием укрепляют стебель и снижают полегание, улучшают фотосинтез и усвоение азота, калия, кальция и магния, повышают устойчивость к засухе, заморозкам и грибным инфекциям</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>0,2 л/га, до 3 обработок за вегетацию</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>Все сельхозкультуры. Зерновые — снижение риска полегания · томаты (подтверждено)</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>раствор</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>рН 11–12</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница;Ячмень;Рапс;Подсолнечник;Соя;Кукуруза;Горох;Гречиха;Лён;Свёкла;Картофель;Овощи</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>офсайт: relict-dv.ru · каталог производителя</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Реликт М Молибден</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Листовые подкормки</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>1340 ₽/л</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr"/>
+      <c r="E53" s="2" t="inlineStr"/>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Молибден (MoO3) 60–70 г/л · азот (N) 25–35 г/л · комплекс аминокислот 100–120 г/л · рН 8–9,5</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Молибден с аминокислотами: стимулирует клубеньковые бактерии и фиксацию азота, помогает синтезу белка и его качеству в семенах, улучшает поглощение фосфора</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>Обработка семян 0,5 л/т · листовая подкормка 0,2–0,4 л/га</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>Бобовые (ключевая роль в усвоении азота), соя, клевер · все сельхозкультуры</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>раствор</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>рН 8–9,5</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница;Ячмень;Рапс;Подсолнечник;Соя;Кукуруза;Горох;Гречиха;Лён;Свёкла;Картофель;Овощи</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>офсайт: relict-dv.ru · каталог производителя</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Реликт М Сера</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Листовые подкормки</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>730 ₽/л</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr"/>
+      <c r="E54" s="2" t="inlineStr"/>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Сера (SO3) 550–600 г/л · азот (N) 110–130 г/л · рН 5–6. Сульфитная форма</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Сера участвует в образовании белков, ферментов и эфирных масел, улучшает усвоение азота, повышает качество зерна злаковых и содержание незаменимых аминокислот в кормовых культурах</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>0,5 л/га листовая подкормка (рапс — фазы розетка, стеблевание, бутонизация)</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>Рапс, соя, капуста и другие серолюбивые культуры · зерновые — качество зерна</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>раствор</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>рН 5–6</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница;Ячмень;Рапс;Соя</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>офсайт: relict-dv.ru · каталог производителя</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Реликт М Цинк</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Листовые подкормки</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>695 ₽/л</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr"/>
+      <c r="E55" s="2" t="inlineStr"/>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Цинк (ZnO) 120–140 г/л · азот (N) 30–40 г/л · комплекс аминокислот 15–180 г/л · рН 5–6</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Цинк с аминокислотами: синтез белков, витаминов и ауксинов, обмен углеводов и фосфора, завязывание и форма плодов, защита белков и липидов от окисления, водоудерживающая способность клеток</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>0,43–1,0 л/га листовая подкормка</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>Кукуруза (3–5 лист, 4 лист при гербицидной обработке) · все сельхозкультуры</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>раствор</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>рН 5–6</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница;Ячмень;Рапс;Подсолнечник;Соя;Кукуруза;Горох;Гречиха;Лён;Свёкла;Картофель;Овощи</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>офсайт: relict-dv.ru · каталог производителя</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Реликт Р</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Листовые подкормки</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>615 ₽/л</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr"/>
+      <c r="E56" s="2" t="inlineStr"/>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Соли гуминовых и фульвовых кислот 4–6% (40–60 г/л) · N общий 0,2–0,5% · N аммонийный 0,1–0,25% · P общий 0,2–0,35% · K общий 0,2–0,35% · рН 9,0–11</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Соли гуминовых и фульвовых кислот: улучшают питание проростка, усиливают иммунный ответ на почвенные патогены, повышают содержание хлорофилла, снижают вред от засухи и гербицидного стресса</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>Обработка семян 0,4 л/т · листовые подкормки — по схеме, часто в баковой смеси с «Реликт М»</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>Все сельхозкультуры. Подтверждено на клевере, яровом рапсе, кукурузе</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>Жидкость, рН 9,0–11</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница;Ячмень;Рапс;Подсолнечник;Соя;Кукуруза;Горох;Гречиха;Лён;Свёкла;Картофель;Овощи</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>офсайт: relict-dv.ru · каталог производителя</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Страда K</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Листовые подкормки</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>332,5 ₽/л</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr"/>
+      <c r="E57" s="2" t="inlineStr"/>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>K2O 152 · N 51 · P2O5 63 · SO3 44,2 · Fe 0,25 · Mn 2,4 · B 0,11 · Zn 0,063 · Cu 0,063 · Mo 0,013 · Co 0,013 · Se 0,013 г/л. 12 элементов питания</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Калий 152 г/л с микроэлементами и кремнием: участвует в синтезе углеводов и их оттоке из листьев в семена, клубни и плоды · смачиватель и прилипатель удерживают раствор на листе</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>3–5 л/га (стандарт 3 л/га). Рабочий раствор 100–300 л/га</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>Кукуруза (трубкование), подсолнечник (формирование корзинки), сах. свёкла, зернобобовые (бутонизация), рис, картофель (после цветения)</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>Плотность 1,3 г/см³</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>Подсолнечник;Кукуруза;Картофель;Свёкла</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>офсайт: volskybiochem.com · каталог производителя</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Страда N</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Листовые подкормки</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>409,5 ₽/л</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr"/>
+      <c r="E58" s="2" t="inlineStr"/>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>N 374 · P2O5 28 · K2O 42 · MgO 2,1 · SO3 17,5 · Fe 0,42 · Mn 0,7 · B 0,22 · Zn 1,8 · Cu 0,83 · Mo 0,7 · Co 0,014 · Se 0,014 г/л · + органические кислоты, витамины, кремний</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Азот в трёх формах и хелаты микроэлементов с проникающим агентом: ускоряет перевод азота в органическую форму, усиливает синтез аминокислот и белков, кремний укрепляет соломину против полегания</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>3–5 л/га (стандарт 3 л/га). Рабочий раствор 100–300 л/га</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>Кукуруза (5–9 лист, трубкование), подсолнечник (4–5 пар листьев), сах. свёкла, зернобобовые, озимые и яровые зерновые (кущение, колошение), картофель</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>Суспензия, 374 г/л азота</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница;Ячмень;Подсолнечник;Кукуруза;Картофель;Свёкла</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>офсайт: volskybiochem.com · каталог производителя</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Страда P</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Листовые подкормки</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>577,5 ₽/л</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr"/>
+      <c r="E59" s="2" t="inlineStr"/>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>N 65 · P2O5 258 · K2O 65 · MgO 2,3 · SO3 10,3 · Fe 0,9 · Mn 0,65 · B 0,26 · Zn 2,1 · Cu 0,9 · Mo 0,65 · Co 0,13 · Se 0,026 г/л</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Фосфор 258 г/л с микроэлементами: входит в состав АТФ и фитина, кремний повышает доступность фосфора, стимулирует цветение, опыление и созревание, развивает корневую систему</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>3–5 л/га (стандарт 3 л/га) · картофель 5 л/га при обработке клубней. Рабочий раствор 100–300 л/га</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>Кукуруза (5–7 лист), подсолнечник, сах. свёкла, зернобобовые, зерновые (кущение — колошение), картофель</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>Стимулирует развитие корневой системы</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница;Ячмень;Подсолнечник;Кукуруза;Картофель;Свёкла</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>офсайт: volskybiochem.com · каталог производителя</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Микромак</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Обработка семян</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>645,7 ₽/л</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr"/>
+      <c r="E60" s="2" t="inlineStr"/>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>17 элементов питания: 5 макро- и 12 микроэлементов в хелатной форме (в т.ч. ванадий — катализатор азотфиксации). 23 индивидуальных состава под конкретные культуры</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>Подаёт микроэлементы на ранних стадиях, когда растение уязвимо: повышает всасывающую способность корней и активность ферментов зародыша · ванадий в составе — катализатор азотфиксации</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>Семена 2 л/т (1 л состава А + 1 л состава Б), рабочий раствор 10 л/т · клубни 0,5 л/т, рабочий раствор 30 л/т</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>Обработка семян всех полевых культур</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>Плотность 1,3 г/см³</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница;Ячмень;Рапс;Подсолнечник;Соя;Кукуруза;Горох;Гречиха;Лён;Свёкла;Картофель;Овощи</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>офсайт: volskybiochem.com · каталог производителя</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Реликт Р Старт (протравитель)</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Обработка семян</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>735 ₽/л</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr"/>
+      <c r="E61" s="2" t="inlineStr"/>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>Гуминовые и фульвокислоты 4–6% · хелатные микроэлементы (Mg, Fe, Mn, Cu, Zn) ≥0,4% · консорциум 4 штаммов рода Bacillus, титр ≥1×10⁷</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>Соли гуминовых и фульвовых кислот для предпосевной обработки: стимулируют прорастание и рост корней, активизируют почвенные микроорганизмы, сдерживающие почвенно-семенные инфекции</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>Предпосевная обработка семян зерновых колосовых, обработка клубней и посадочного материала · возможны листовые обработки в вегетацию</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница, ячмень, рожь, картофель. Пролонгированная защита от корневых гнилей злаковых и ризоктониоза картофеля</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница;Ячмень;Картофель</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>офсайт: relictorganics.com · каталог производителя</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Экомак</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Обработка семян</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>724,5 ₽/л</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr"/>
+      <c r="E62" s="2" t="inlineStr"/>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>N 2,4 · P2O5 0,61 · K2O 1,77 · MgO 0,97 · SO3 4,9 · Fe 0,35 · Mn 0,58 · B 0,35 · Zn 0,98 · Cu 0,97 · Mo 0,09 · Co 0,18 (% мас.) · микро — хелат ОЭДФ. 12 элементов + полимерные прилипатели</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Полимерная композиция закрепляет препарат на семенах, осмотически активные вещества ускоряют поступление элементов и влаги внутрь: всходы дружнее, корни мощнее, прорастание шире по температуре</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>Семена 0,5 л/т (рабочий раствор 10 л/т) · клубни 0,2 л/т (рабочий раствор 30 л/т)</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>Предпосевная обработка семян и клубней</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>Плотность 1,2 г/см³</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница;Ячмень;Рапс;Подсолнечник;Соя;Кукуруза;Горох;Гречиха;Лён;Свёкла;Картофель;Овощи</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>офсайт: volskybiochem.com · каталог производителя</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Анкер Трио, КС</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Протравители</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>1475 ₽/л</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Твёрдая и пыльная головня, фузариозная и гельминтоспориозная корневые гнили, плесневение семян</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>тиабендазол 60 г/л + тебуконазол 60 г/л + имазалил 40 г/л</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr"/>
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>0,4–0,5 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница яровая/озимая, ячмень яровой/озимый</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>5 л × 4</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница;Ячмень</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>прайс «Сатурн» 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Тиара, КС</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Протравители</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>945 ₽/л</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Хлебная жужелица, внутристеблевые мухи, блошки, тли, цикадки</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>тиаметоксам 350 г/л</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr"/>
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>0,5–1 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница яровая/озимая, ячмень яровой/озимый</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>5 л × 4</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница;Ячмень</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>прайс «Сатурн» 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Тиль Про, КС</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Протравители</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>по запросу</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Хлебная жужелица, внутристеблевые мухи, блошки, тли, цикадки, проволочник, клубеньковый долгоносик</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>тиаметоксам 350 г/л</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr"/>
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>0,5–9 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница яровая/озимая, ячмень яровой/озимый, рожь озимая, подсолнечник, кукуруза, горох, соя, рапс</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>5 л × 4</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница;Ячмень;Рапс;Подсолнечник;Соя;Кукуруза;Горох</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>прайс «Сатурн» 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Тореадор Макси, КС</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Протравители</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>1760 ₽/л</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Проволочники и ложнопроволочники, внутристеблевые мухи, крестоцветные блошки, хлебная жужелица</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>имидаклоприд 600 г/л</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr"/>
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>0,3–12 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница яровая/озимая, ячмень, рапс, кукуруза, подсолнечник</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>5 л × 4</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница;Ячмень;Рапс;Подсолнечник;Кукуруза</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>прайс «Сатурн» 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>FERTIKA Газонное Весна-Лето NPK 11-12-26</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Удобрения</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>96 ₽/кг</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr"/>
+      <c r="E67" s="2" t="inlineStr"/>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>N 11 · P2O5 12 · K2O 26 · Ca 0,55 · MgO 0,4 · SO3 0,7 · B 0,09 · Cu 0,08 · Fe 0,16 · Mn 0,16 · Mo 0,008 · Zn 0,09 (%)</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>Быстро растворимые гранулы без пыли: ускоряет отрастание трав после скашивания, повышает густоту травостоя, препятствует мху и сорнякам, даёт ярко-зелёную окраску</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>Закладка газона 10 кг/100 м² · весенняя подкормка 4–5 кг/100 м² · в вегетацию 5–7 кг/100 м²</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>Газон</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>800 кг</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>Гранулированное</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>каталог производителя</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>FERTIKA Газонное. Осень</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Удобрения</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>97 ₽/кг</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr"/>
+      <c r="E68" s="2" t="inlineStr"/>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>NPK 6:13:36 + микроэлементы — Ca, MgO, SO3, B, Cu, Fe, Mn, Mo, Zn</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Осенняя подкормка газона: повышенные фосфор и калий обеспечивают укоренение травосмесей, формирование корневой системы и лучшую перезимовку · азот осенью не разгоняет рост под заморозки</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>Закладка газона 10 кг/100 м² · по вегетации 7 кг/100 м²</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>Газон</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>водорастворимые гранулы, 800 кг</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>офсайт: fertika.com · прайс «Сатурн» 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>FERTIKA Картофельное-5 NPK 11-9-16</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Удобрения</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>110 ₽/кг</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr"/>
+      <c r="E69" s="2" t="inlineStr"/>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>N 11 · P2O5 9 · K2O 16 · Ca 0,55 · MgO 1 · SO3 4 · B 0,09 · Cu 0,08 · Mn 0,16 (%)</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Состав подобран под картофель: стимулирует клубнеобразование, не приводит к накоплению нитратов, калий улучшает лёжкость клубней, сера и магний увеличивают их количество</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>Картофель 600–800 кг/га</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>Картофель</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>800 кг</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>Без хлора</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>Картофель</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>каталог производителя</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>FERTIKA Листовое 10-5-40</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Удобрения</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>222 ₽/кг</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr"/>
+      <c r="E70" s="2" t="inlineStr"/>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>N 10,1 · P2O5 5 · K2O 40 · MgO 0,5 · S 4,4 · B 0,03 · Cu 0,01 · Fe 0,15 · Mn 0,14 · Mo 0,003 · Zn 0,01 (%)</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Повышенный калий на завершающих стадиях: интенсивное плодоношение и равномерное созревание, накопление сахаров, крахмала и белка, оптимизация водного режима и устойчивость к засухе</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>Некорневая подкормка 2–5 кг/га. Фертигация: теплицы 0,05–0,2%, открытый грунт 0,1–0,2%</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>Масличные (бутонизация), зерновые (флаговый лист — колошение), картофель (рост клубней), виноград 2–5 (начало созревания ягод), овощи 3–5 (созревание)</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>25 кг</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>100% растворимость · ЕС 0,1% р-ра 1,1 мСм/см · рН 1% р-ра 6</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница;Ячмень;Картофель;Овощи</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>каталог производителя</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>FERTIKA Листовое 18-18-18</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Удобрения</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>202 ₽/кг</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr"/>
+      <c r="E71" s="2" t="inlineStr"/>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>N 18 · P2O5 18 · K2O 18 · MgO 1,4 · S 1,8 · B 0,03 · Cu 0,01 · Fe 0,15 · Mn 0,14 · Mo 0,003 · Zn 0,01 (%) · микро — хелат ЭДТА</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Равновесное NPK для питания на всех стадиях: стимулирует рост и фотосинтез, снимает стресс от пестицидов, вредителей, засухи, переувлажнения и заморозков</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>Некорневая подкормка 2–5 кг/га. Фертигация: теплицы 0,05–0,2%, открытый грунт 0,1–0,2%</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>Зерновые 2–4 (кущение, выход в трубку), кукуруза 2–3 (5–6 листьев), подсолнечник 2–4 (8–10 листьев), рапс 2–5 (6–8 листьев), картофель 2–4 (формирование клубней), бобовые 2–4 (перед цветением)</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>25 кг</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>100% растворимость · ЕС 0,1% р-ра 0,9 мСм/см · рН 1% р-ра 5</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница;Ячмень;Рапс;Подсолнечник;Кукуруза;Картофель</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>каталог производителя</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>FERTIKA Листовое 19-6-20</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Удобрения</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>196 ₽/кг</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr"/>
+      <c r="E72" s="2" t="inlineStr"/>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>N 19 · P2O5 6 · K2O 20 · MgO 3 · S 7 · B 0,03 · Cu 0,01 · Fe 0,1 · Mn 0,1 · Mo 0,003 · Zn 0,01 (%)</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Для декоративных, цветочных, ягодных и овощных культур и некорневых подкормок полевых: применимо при фертигации на всех типах орошения, совместимо с большинством пестицидов</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>Некорневая подкормка 2–3 кг/га. Фертигация: теплицы 0,05–0,2%, открытый грунт 0,1–0,2%</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>Цветочно-декоративные, ягодные, овощные, зелень · полевые — зерновые и рапс 2–3 (начало созревания)</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>25 кг</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>100% растворимость · ЕС 0,1% р-ра 0,9 мСм/см · рН 1% р-ра 5</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница;Ячмень;Рапс;Овощи</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>каталог производителя</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>FERTIKA Листовое 4-13-36</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Удобрения</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>232 ₽/кг</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr"/>
+      <c r="E73" s="2" t="inlineStr"/>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>N 4 · P2O5 13 · K2O 36 · MgO 1,6 · S 7,7 · B 0,02 · Cu 0,01 · Fe 0,1 · Mn 0,1 · Mo 0,002 · Zn 0,01 (%)</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Бесхлорное удобрение с повышенным калием и микроэлементами в хелатной форме для второй половины вегетации, корневых и некорневых подкормок · повышает устойчивость к стрессам</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>Некорневая подкормка 2–5 кг/га. Фертигация: теплицы 0,05–0,2%, открытый грунт 0,1–0,2%</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>Масличные (бутонизация), зерновые (флаговый лист — колошение), сахарная свёкла (до смыкания рядков), картофель (рост клубней), бобовые (формирование бобов), овощи 3–5 (созревание)</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>25 кг</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>100% растворимость · ЕС 0,1% р-ра 1,1 мСм/см · рН 1% р-ра 6</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница;Ячмень;Картофель;Свёкла;Овощи</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>каталог производителя</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>FERTIKA Листовое Старт 13-40-13</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Удобрения</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>227 ₽/кг</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr"/>
+      <c r="E74" s="2" t="inlineStr"/>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>N 12,9 · P2O5 40 · K2O 13,4 · MgO 0,1 · S 0,02 · B 0,015 · Cu 0,03 · Fe 0,08 · Mn 0,08 · Mo 0,003 · Zn 0,03 (%) · микро — хелат ЭДТА</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Повышенный фосфор на старте: стимулирует развитие корневой системы, активирует клеточное деление и обмен веществ · в бутонизацию и цветение ускоряет образование репродуктивных органов</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>Некорневая подкормка 2–4 кг/га. Фертигация: теплицы 0,05–0,2% (0,5–2 кг/1000 л), открытый грунт 0,1–0,2% (1–2 кг/1000 л)</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>Зерновые (начало кущения), кукуруза (3–5 листьев), подсолнечник (3–4 листа), рапс (3–4 листа), картофель 2–5 кг/га (клубнеобразование)</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>25 кг</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>100% растворимость · ЕС 0,1% р-ра 1,0 мСм/см · рН 1% р-ра 5</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница;Ячмень;Рапс;Подсолнечник;Кукуруза;Картофель</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>каталог производителя</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>FERTIKA Осеннее NPK 5-21-31</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Удобрения</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>106 ₽/кг</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr"/>
+      <c r="E75" s="2" t="inlineStr"/>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>N 5 · P2O5 21 · K2O 31 · Ca 0,55 · MgO 0,5 · S 0,7 · B 0,09 · Cu 0,08 · Fe 0,16 · Mn 0,16 · Mo 0,008 · Zn 0,09 (%)</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Гранулированное удобрение под полевые культуры для основной обработки почвы осенью: повышенные фосфор и калий, нужные растениям в осенний период, прочные гранулы для равномерного внесения</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>Сахарная свёкла 300–600 кг/га · подсолнечник 200–300 · озимая пшеница 200–400 · кукуруза на зерно 400–600 кг/га</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>Полевые культуры — основное внесение осенью</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>800 кг</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>Гранулы прочные, одного размера</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница;Ячмень;Рапс;Подсолнечник;Соя;Кукуруза;Горох;Гречиха;Лён;Свёкла;Картофель;Овощи</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>каталог производителя</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>FERTIKA Плюс 12-11-26</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Удобрения</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>207 ₽/кг</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr"/>
+      <c r="E76" s="2" t="inlineStr"/>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>N 12,3 · P2O5 11 · K2O 26 · MgO 2,5 · S 3,3 · B 0,02 · Cu 0,01 · Fe 0,1 · Mn 0,1 · Mo 0,002 · Zn 0,01 (%)</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Бесхлорное водорастворимое удобрение с хелатными микроэлементами для всех субстратов и типов полива, корневых и некорневых подкормок · повышает устойчивость к стрессам</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>Некорневая подкормка 2–3 кг/га. Фертигация: теплицы 0,05–0,2%, открытый грунт 0,1–0,2%</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>Цветы, овощи, ягоды, зелень · зерновые и подсолнечник 2–3 (начало созревания)</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>25 кг</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>100% растворимость · ЕС 0,1% р-ра 1,0 мСм/см · рН 1% р-ра 5</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница;Ячмень;Подсолнечник;Овощи</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>каталог производителя</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>FERTIKA Плюс 16-20-27</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Удобрения</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>203 ₽/кг</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr"/>
+      <c r="E77" s="2" t="inlineStr"/>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>N 16 · P2O5 20 · K2O 27 · B 0,02 · Cu 0,01 · Fe 0,1 · Mn 0,1 · Zn 0,01 (%)</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>Полностью растворимое NPK с микроэлементами: подкормки в период корнеобразования и цветения, улучшает вкусовые свойства и устойчивость к болезням</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>Фертигация: теплицы 0,05–0,2%, открытый грунт 0,1–0,2% · корневые и некорневые подкормки</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>Цветы, ягоды, зелень — все субстраты, почвы и грунты, все типы полива</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>25 кг</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>100% растворимость</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>Овощи</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>каталог производителя</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>FERTIKA Плюс 6,4-11-31</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Удобрения</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>225 ₽/кг</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr"/>
+      <c r="E78" s="2" t="inlineStr"/>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>N 6,4 · P2O5 11 · K2O 31 · MgO 2,6 · S 4,4 · B 0,02 · Cu 0,01 · Fe 0,1 · Mn 0,1 · Mo 0,002 · Zn 0,01 (%)</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Бесхлорное удобрение с повышенным калием и хелатными микроэлементами для фертигации: защищённый грунт, гидропоника, инертные и органические субстраты, ягоды, овощи и сады</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>Фертигация и гидропоника: теплицы 0,05–0,2%, открытый грунт 0,1–0,2%</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>Огурец, томат, цветы, ягоды — защищённый и открытый грунт, все типы полива</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>25 кг</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>100% растворимость · ЕС 0,1% р-ра 1,0 мСм/см · рН 1% р-ра 6</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>Овощи</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>каталог производителя</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>FERTIKA Сульфат калия</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Удобрения</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>103 ₽/кг</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr"/>
+      <c r="E79" s="2" t="inlineStr"/>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>K2O 50 · S 17 (%)</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Калий без хлора: снижает нагрузку на чувствительные к хлору и молодые растения, увеличивает размер и плотность плодов, содержание сахара и пигментов, устойчивость к засухе и к хранению</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>Томаты, огурцы, цветочные 15–20 г/м² · картофель, капуста, свёкла, морковь 25–30 г/м² · редис, лук, салат 5–10 г/м² · защищённый грунт 30–40 г/м² · плодовые деревья 150–200 г/растение</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>Плодовые, ягодные, овощные, чувствительные к хлору культуры</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>МКР 1000 кг / мешки 35 кг</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>Бесхлорное</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>Овощи</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>каталог производителя</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>FERTIKA Универсал-2 NPK 12-8-14</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Удобрения</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>112 ₽/кг</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr"/>
+      <c r="E80" s="2" t="inlineStr"/>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>N 12 · P2O5 8 · K2O 14 · Ca 0,6 · MgO 2 · SO3 8 · B 0,09 · Cu 0,08 · Fe 0,16 · Mn 0,16 · Mo 0,08 · Zn 0,09 (%)</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Гранулированное удобрение для овощных и плодово-ягодных: микроэлементы ускоряют развитие, снижают риск грибных и бактериальных болезней, калий улучшает лёжкость</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>Картофель 600–800 кг/га · овощные 600–1000 кг/га · ягодные 200–400 кг/га · декоративные 600–800 кг/га</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>Картофель, овощные, ягодные, декоративные культуры</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>800 кг</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>Гранулы, не пылят</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>Картофель;Овощи</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>каталог производителя</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>FERTIKA Хвойное для вечнозелёных Весна-Лето NPK 10-7-14</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Удобрения</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>по запросу</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr"/>
+      <c r="E81" s="2" t="inlineStr"/>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>N 9,9 · P2O5 7 · K2O 14 · MgO 6,9 · SO3 40,8 · B 0,05 · Cu 0,03 · Mn 0,1 · Zn 0,06 (%)</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>Гранулированное удобрение пролонгированного действия без хлора для хвойных, рододендронов, гортензий и голубики: понижает pH почвы до нужного уровня, даёт насыщенный цвет хвои</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>При посадке и подкормке 30–40 г на растение · поверхностно 60 г/м², 1–2 раза за вегетацию</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>Хвойные, рододендроны, азалии, гортензии, голубика, садовая черника</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>800 кг, 40 кг</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>Пролонгированное действие, понижает рН почвы, без хлора</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>каталог производителя</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>FERTIKA Эко Калий</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Удобрения</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>48 ₽/кг</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr"/>
+      <c r="E82" s="2" t="inlineStr"/>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>K2O 37 · P2O5 4,1 · SO3 10 · MgO 7,1 · CaO 7,1 · Fe 0,1 · Mn 0,01 · Zn 0,02 · Cu 0,02 (%)</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>Бесхлорный калий растительного происхождения из лузги подсолнечника с повышенным магнием и серой: для почв, бедных магнием, и культур, чувствительных к хлору</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>Яровые зерновые, кукуруза, рапс, подсолнечник, озимая пшеница 200–400 кг/га · картофель и корнеплоды 300–350 · томат, огурец, плодово-ягодные 200–250 кг/га</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>Зерновые, кукуруза, рапс, подсолнечник, картофель, корнеплоды, плодово-ягодные</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>МКР / 25 кг</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>Бесхлорное, растительного происхождения (лузга подсолнечника)</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница;Ячмень;Рапс;Подсолнечник;Кукуруза;Картофель</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>каталог производителя</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Relict Макро N Mg+</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Удобрения</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>по запросу</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr"/>
+      <c r="E83" s="2" t="inlineStr"/>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>Азот общий 250–280 г/л · сера (SO3) 40–50 г/л · магний (MgO) 7–10 г/л · плотность 1,2–1,3 г/см³, рН 5,5–7,5</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>Источник азотного питания с выверенным соотношением азота, серы и магния: оптимизирует азотный обмен, усиливает усвоение других макро- и микроэлементов, снижает риск хлороза</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>Листовая подкормка</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>Все декоративные и сельскохозяйственные культуры</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>Плотность 1,2–1,3 г/см³, рН 5,5–7,5</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница;Ячмень;Рапс;Подсолнечник;Соя;Кукуруза;Горох;Гречиха;Лён;Свёкла;Картофель;Овощи</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>каталог производителя</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Relict Макро PK</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Удобрения</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>по запросу</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr"/>
+      <c r="E84" s="2" t="inlineStr"/>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Азот общий 65–90 г/л · фосфор (P2O5) 410–450 г/л · калий (K2O) 140–150 г/л · плотность 1,35–1,45 г/см³, рН 6,5–7,5</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Насыщенный усваиваемыми фосфат-ионами раствор: оптимизирует обменные процессы, устраняет дисбаланс по макроэлементам, способствует накоплению сахаров и сухих веществ, улучшает лёжкость урожая</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>Листовая подкормка</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>Все культуры · особенно масличные — подсолнечник, рапс, соя</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>Плотность 1,35–1,45 г/см³, рН 6,5–7,5</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница;Ячмень;Рапс;Подсолнечник;Соя;Кукуруза;Горох;Гречиха;Лён;Свёкла;Картофель;Овощи</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>каталог производителя</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Атлант Супер</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Фунгициды</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>по запросу</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Мучнистая роса, ржавчина (бурая, жёлтая, стеблевая), септориоз, пиренофороз, фузариоз (частично), церкоспороз, фомоз, альтернариоз</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>пропиконазол 250 г/л + ципроконазол 80 г/л</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr"/>
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>0,4–0,75 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница яровая/озимая, свёкла сахарная</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>5 л × 4</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница;Свёкла</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>прайс «Сатурн» 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Гранберг Про, КЭ</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Фунгициды</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>1562,5 ₽/л</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Ржавчина бурая, стеблевая, жёлтая · мучнистая роса, септориоз листьев и колоса, пиренофороз, карликовая ржавчина, ринхоспориоз, сетчатая и тёмно-бурая пятнистости, церкоспороз, фомоз, оидиум, альтернариоз, аскохитоз, антракноз</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>пропиконазол 300 г/л + тебуконазол 200 г/л</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr"/>
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>0,2–0,6 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница яровая/озимая, ячмень яровой/озимый, свёкла сахарная, виноград, рапс яровой/озимый, соя</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>10 л × 2</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница;Ячмень;Рапс;Соя;Свёкла</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>прайс «Сатурн» 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Гранберг, КЭ</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Фунгициды</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>1417,5 ₽/л</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Ржавчина бурая, стеблевая, жёлтая, корончатая · мучнистая роса, септориоз листьев и колоса, пиренофороз, карликовая ржавчина, сетчатая, тёмно-бурая и красно-бурая пятнистости, ринхоспориоз, альтернариоз, склеротиниоз</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>тебуконазол 250 г/л</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr"/>
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>0,75–1 л (кг)/га</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница яровая/озимая, ячмень яровой/озимый, рожь озимая, овёс, рапс яровой/озимый</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>10 л × 2</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>Пшеница;Ячмень;Рапс</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>прайс «Сатурн» 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Волски Аминатор</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>900 ₽</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr"/>
+      <c r="E88" s="2" t="inlineStr"/>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>— позиции нет в новой выгрузке —</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr"/>
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>нет в прайсе 13.10 — только на сайте</t>
         </is>
       </c>
     </row>
